--- a/src/attributions/attributions_ig_traj_184.xlsx
+++ b/src/attributions/attributions_ig_traj_184.xlsx
@@ -999,19 +999,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.174700405265382</v>
+        <v>0.06878495572301925</v>
       </c>
       <c r="C2" t="n">
         <v>-0</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.06380857082925832</v>
+        <v>-0.03069151734102177</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.003507805380645707</v>
+        <v>-0.02571446354943899</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -1026,19 +1026,19 @@
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1406186874732371</v>
+        <v>0.077366653335551</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06485538403779992</v>
+        <v>-0.04087286931184206</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.02745726746022301</v>
+        <v>-0.04346325929529007</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -1056,22 +1056,22 @@
         <v>-0</v>
       </c>
       <c r="T2" t="n">
-        <v>0.1173228857484364</v>
+        <v>0.04878917665407379</v>
       </c>
       <c r="U2" t="n">
         <v>0</v>
       </c>
       <c r="V2" t="n">
-        <v>0.008178756730846939</v>
+        <v>-0.009443537803602345</v>
       </c>
       <c r="W2" t="n">
-        <v>0.03000568214549158</v>
+        <v>-0.008768059549458753</v>
       </c>
       <c r="X2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z2" t="n">
         <v>0</v>
@@ -1083,22 +1083,22 @@
         <v>-0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.155591944093968</v>
+        <v>-0.009624295813328283</v>
       </c>
       <c r="AD2" t="n">
         <v>-0</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.002293365829096008</v>
+        <v>-0.02811822496536106</v>
       </c>
       <c r="AF2" t="n">
-        <v>-0.05789719831329076</v>
+        <v>-0.04428621159754786</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI2" t="n">
         <v>-0</v>
@@ -1107,52 +1107,52 @@
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.05282793404335004</v>
+        <v>0.03804761946090485</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN2" t="n">
-        <v>-0.04150033825488542</v>
+        <v>0.00719172513601007</v>
       </c>
       <c r="AO2" t="n">
-        <v>-0.04759543746856326</v>
+        <v>0.05737656672954088</v>
       </c>
       <c r="AP2" t="n">
         <v>0</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5032384398965168</v>
+        <v>0.2250673685840331</v>
       </c>
       <c r="AV2" t="n">
         <v>-0</v>
       </c>
       <c r="AW2" t="n">
-        <v>-0.04135005681471981</v>
+        <v>-0.1260100887775259</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.1068583468469537</v>
+        <v>-0.0362815329312914</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA2" t="n">
         <v>-0</v>
@@ -1161,49 +1161,49 @@
         <v>0</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.1016045784362324</v>
+        <v>-0.04978825673996076</v>
       </c>
       <c r="BE2" t="n">
         <v>0</v>
       </c>
       <c r="BF2" t="n">
-        <v>-0.137508144624918</v>
+        <v>-0.01047460973829414</v>
       </c>
       <c r="BG2" t="n">
-        <v>-0.1878961019788547</v>
+        <v>-0.05504961132270558</v>
       </c>
       <c r="BH2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
       <c r="BK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.07925132324931515</v>
+        <v>-0.04520365544380526</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.05288635029369224</v>
+        <v>0.02328311757296118</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.1582625186264903</v>
+        <v>0.06783940532806565</v>
       </c>
       <c r="BQ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR2" t="n">
         <v>0</v>
@@ -1218,16 +1218,16 @@
         <v>-0</v>
       </c>
       <c r="BV2" t="n">
-        <v>0.2355773419519716</v>
+        <v>0.1453693542215246</v>
       </c>
       <c r="BW2" t="n">
         <v>0</v>
       </c>
       <c r="BX2" t="n">
-        <v>-0.008443877036823968</v>
+        <v>-0.06941258813521545</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.05887835685151704</v>
+        <v>-0.02084371496253373</v>
       </c>
       <c r="BZ2" t="n">
         <v>0</v>
@@ -1236,169 +1236,169 @@
         <v>-0</v>
       </c>
       <c r="CB2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="n">
         <v>0</v>
       </c>
       <c r="CD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE2" t="n">
-        <v>-0.1188987571164323</v>
+        <v>-0.06773199727171474</v>
       </c>
       <c r="CF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG2" t="n">
-        <v>0.05366862721949494</v>
+        <v>0.0323309002694922</v>
       </c>
       <c r="CH2" t="n">
-        <v>-0.03613873916058442</v>
+        <v>0.03081989762133092</v>
       </c>
       <c r="CI2" t="n">
         <v>-0</v>
       </c>
       <c r="CJ2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK2" t="n">
         <v>0</v>
       </c>
       <c r="CL2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM2" t="n">
         <v>0</v>
       </c>
       <c r="CN2" t="n">
-        <v>0.01298989803545897</v>
+        <v>0.008847202425541855</v>
       </c>
       <c r="CO2" t="n">
         <v>-0</v>
       </c>
       <c r="CP2" t="n">
-        <v>0.03104349447185514</v>
+        <v>-0.02250682526899448</v>
       </c>
       <c r="CQ2" t="n">
-        <v>0.02731838831695704</v>
+        <v>-0.003952919338119351</v>
       </c>
       <c r="CR2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS2" t="n">
         <v>-0</v>
       </c>
       <c r="CT2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW2" t="n">
-        <v>-0.1102090945367697</v>
+        <v>-0.08041130529596101</v>
       </c>
       <c r="CX2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY2" t="n">
-        <v>0.0826327873815951</v>
+        <v>0.03733434590718204</v>
       </c>
       <c r="CZ2" t="n">
-        <v>-0.02950060512470363</v>
+        <v>0.03958730472799894</v>
       </c>
       <c r="DA2" t="n">
         <v>0</v>
       </c>
       <c r="DB2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC2" t="n">
         <v>0</v>
       </c>
       <c r="DD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>-0.07218043357868932</v>
+        <v>-0.04211822986753157</v>
       </c>
       <c r="DG2" t="n">
         <v>0</v>
       </c>
       <c r="DH2" t="n">
-        <v>0.0723749077914128</v>
+        <v>0.02515581411221802</v>
       </c>
       <c r="DI2" t="n">
-        <v>-0.07927329742842945</v>
+        <v>-0.09486238766804048</v>
       </c>
       <c r="DJ2" t="n">
         <v>-0</v>
       </c>
       <c r="DK2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DO2" t="n">
-        <v>0.01695950829425642</v>
+        <v>0.06199002231732997</v>
       </c>
       <c r="DP2" t="n">
         <v>0</v>
       </c>
       <c r="DQ2" t="n">
-        <v>-0.06909687788480308</v>
+        <v>0.008325475000102377</v>
       </c>
       <c r="DR2" t="n">
-        <v>-0.03907078061034578</v>
+        <v>0.003641888216754151</v>
       </c>
       <c r="DS2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT2" t="n">
         <v>-0</v>
       </c>
       <c r="DU2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV2" t="n">
         <v>0</v>
       </c>
       <c r="DW2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DX2" t="n">
-        <v>-0.1077367051459334</v>
+        <v>0.02080111300231256</v>
       </c>
       <c r="DY2" t="n">
         <v>0</v>
       </c>
       <c r="DZ2" t="n">
-        <v>0.02503691602514511</v>
+        <v>0.01083171903933087</v>
       </c>
       <c r="EA2" t="n">
-        <v>0.005152914857965548</v>
+        <v>-0.01211005040968041</v>
       </c>
       <c r="EB2" t="n">
         <v>-0</v>
       </c>
       <c r="EC2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE2" t="n">
         <v>-0</v>
@@ -1407,22 +1407,22 @@
         <v>0</v>
       </c>
       <c r="EG2" t="n">
-        <v>-0.08859188860541055</v>
+        <v>-0.03400763588803322</v>
       </c>
       <c r="EH2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI2" t="n">
-        <v>0.08348058255145799</v>
+        <v>0.02077022506980593</v>
       </c>
       <c r="EJ2" t="n">
-        <v>0.06443491511551408</v>
+        <v>0.02673818141033983</v>
       </c>
       <c r="EK2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM2" t="n">
         <v>-0</v>
@@ -1434,25 +1434,25 @@
         <v>0</v>
       </c>
       <c r="EP2" t="n">
-        <v>-0.08092313944385021</v>
+        <v>-0.05097971460466226</v>
       </c>
       <c r="EQ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER2" t="n">
-        <v>0.09689442380757295</v>
+        <v>0.02956188427634206</v>
       </c>
       <c r="ES2" t="n">
-        <v>-0.05172902457997552</v>
+        <v>-0.02888374562974486</v>
       </c>
       <c r="ET2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EW2" t="n">
         <v>-0</v>
@@ -1461,109 +1461,109 @@
         <v>0</v>
       </c>
       <c r="EY2" t="n">
-        <v>-0.1176901670914857</v>
+        <v>-0.08358015591820538</v>
       </c>
       <c r="EZ2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA2" t="n">
-        <v>0.06090830889279625</v>
+        <v>0.04039363668023409</v>
       </c>
       <c r="FB2" t="n">
-        <v>-0.03754008197371184</v>
+        <v>0.02253947693667311</v>
       </c>
       <c r="FC2" t="n">
         <v>-0</v>
       </c>
       <c r="FD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG2" t="n">
         <v>-0</v>
       </c>
       <c r="FH2" t="n">
-        <v>0.007180417775814216</v>
+        <v>-0.06076403252423403</v>
       </c>
       <c r="FI2" t="n">
         <v>-0</v>
       </c>
       <c r="FJ2" t="n">
-        <v>-0.04337617579059089</v>
+        <v>-0.0154113169000024</v>
       </c>
       <c r="FK2" t="n">
-        <v>-0.1112941919735643</v>
+        <v>0.07609998584875978</v>
       </c>
       <c r="FL2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FM2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FN2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FO2" t="n">
         <v>0</v>
       </c>
       <c r="FP2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ2" t="n">
-        <v>-0.03827592422328659</v>
+        <v>-0.03323858032217013</v>
       </c>
       <c r="FR2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS2" t="n">
-        <v>0.1153963110583305</v>
+        <v>0.2552096284800174</v>
       </c>
       <c r="FT2" t="n">
-        <v>-0.122125255559709</v>
+        <v>0.1013895058514104</v>
       </c>
       <c r="FU2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV2" t="n">
         <v>-0</v>
       </c>
       <c r="FW2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FX2" t="n">
         <v>0</v>
       </c>
       <c r="FY2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ2" t="n">
-        <v>0.01733865300963978</v>
+        <v>-0.05409512951917171</v>
       </c>
       <c r="GA2" t="n">
         <v>-0</v>
       </c>
       <c r="GB2" t="n">
-        <v>-0.05158432042519943</v>
+        <v>0.02850453996889035</v>
       </c>
       <c r="GC2" t="n">
         <v>0</v>
       </c>
       <c r="GD2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE2" t="n">
         <v>-0</v>
       </c>
       <c r="GF2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -1571,22 +1571,22 @@
         <v>-0</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.04603049495417279</v>
+        <v>-0.1899240976431099</v>
       </c>
       <c r="C3" t="n">
-        <v>0.1155881735669102</v>
+        <v>0.09230288858517598</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.06254345940961646</v>
+        <v>0.03493771418948038</v>
       </c>
       <c r="F3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
         <v>-0</v>
@@ -1598,19 +1598,19 @@
         <v>-0</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.03102622474963415</v>
+        <v>-0.1614401213591474</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09864249804520071</v>
+        <v>0.05056856743259253</v>
       </c>
       <c r="M3" t="n">
         <v>-0</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.04999438399816673</v>
+        <v>0.03635192233300727</v>
       </c>
       <c r="O3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>-0</v>
@@ -1625,43 +1625,43 @@
         <v>0</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0597658244216443</v>
+        <v>-0.08106620150546673</v>
       </c>
       <c r="U3" t="n">
-        <v>0.03335906570210445</v>
+        <v>-0.03301016177385782</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.08349701315270035</v>
+        <v>-0.07491864464309755</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>-0</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC3" t="n">
-        <v>-0.104996663863937</v>
+        <v>-0.1413944889841233</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.001975549789468315</v>
+        <v>0.1354422292907247</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.04178166966866048</v>
+        <v>-0.06592812179542598</v>
       </c>
       <c r="AG3" t="n">
         <v>0</v>
@@ -1670,25 +1670,25 @@
         <v>-0</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.08815195836614717</v>
+        <v>-0.2701434640105959</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.09716141610776273</v>
+        <v>0.08593933028693412</v>
       </c>
       <c r="AN3" t="n">
         <v>0</v>
       </c>
       <c r="AO3" t="n">
-        <v>-0.1131808238335851</v>
+        <v>-0.2304023112405905</v>
       </c>
       <c r="AP3" t="n">
         <v>-0</v>
@@ -1703,25 +1703,25 @@
         <v>-0</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AU3" t="n">
-        <v>-0.1122005962952311</v>
+        <v>-0.4472982358192694</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2481796584168727</v>
+        <v>0.0635689053378367</v>
       </c>
       <c r="AW3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX3" t="n">
-        <v>-0.0486629946673699</v>
+        <v>-0.05801451614831778</v>
       </c>
       <c r="AY3" t="n">
         <v>-0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA3" t="n">
         <v>-0</v>
@@ -1730,46 +1730,46 @@
         <v>-0</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD3" t="n">
-        <v>-0.004270004037403884</v>
+        <v>0.1335796454769523</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0606802730647632</v>
+        <v>0.1679128458229354</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.01875166981834338</v>
+        <v>0.07688155989676267</v>
       </c>
       <c r="BH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BK3" t="n">
         <v>-0</v>
       </c>
       <c r="BL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.01414015706522469</v>
+        <v>0.08413238730692199</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.05522332365676033</v>
+        <v>0.01254493556903384</v>
       </c>
       <c r="BO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BP3" t="n">
-        <v>-0.003673073538533385</v>
+        <v>-0.09901369657011702</v>
       </c>
       <c r="BQ3" t="n">
         <v>0</v>
@@ -1778,61 +1778,61 @@
         <v>0</v>
       </c>
       <c r="BS3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT3" t="n">
         <v>0</v>
       </c>
       <c r="BU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.008732785988838693</v>
+        <v>-0.3208765411562946</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.1680791028370424</v>
+        <v>0.06723869622971948</v>
       </c>
       <c r="BX3" t="n">
         <v>0</v>
       </c>
       <c r="BY3" t="n">
-        <v>-0.1273145449183839</v>
+        <v>0.04832301689888361</v>
       </c>
       <c r="BZ3" t="n">
         <v>-0</v>
       </c>
       <c r="CA3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="n">
         <v>-0</v>
       </c>
       <c r="CC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD3" t="n">
         <v>0</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.05619691507123452</v>
+        <v>0.258080399387357</v>
       </c>
       <c r="CF3" t="n">
-        <v>-0.03558090667521231</v>
+        <v>-0.06295782148832917</v>
       </c>
       <c r="CG3" t="n">
         <v>0</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.02602855815802763</v>
+        <v>-0.01362056050973387</v>
       </c>
       <c r="CI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CJ3" t="n">
         <v>0</v>
       </c>
       <c r="CK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL3" t="n">
         <v>0</v>
@@ -1841,16 +1841,16 @@
         <v>-0</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.004379652505397869</v>
+        <v>-0.03404932116646436</v>
       </c>
       <c r="CO3" t="n">
-        <v>-0.007553606186392568</v>
+        <v>0.01789496198479985</v>
       </c>
       <c r="CP3" t="n">
         <v>0</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.04648457113708529</v>
+        <v>0.01354369596815163</v>
       </c>
       <c r="CR3" t="n">
         <v>0</v>
@@ -1859,34 +1859,34 @@
         <v>0</v>
       </c>
       <c r="CT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.0470959660935891</v>
+        <v>0.2624097377304607</v>
       </c>
       <c r="CX3" t="n">
-        <v>-0.03321711699244952</v>
+        <v>-0.0677543016098367</v>
       </c>
       <c r="CY3" t="n">
         <v>-0</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.04538984449104436</v>
+        <v>-0.008642051451971552</v>
       </c>
       <c r="DA3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DB3" t="n">
         <v>-0</v>
       </c>
       <c r="DC3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD3" t="n">
         <v>-0</v>
@@ -1895,52 +1895,52 @@
         <v>-0</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.007212414910711647</v>
+        <v>0.01583040436876677</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.02007721487956587</v>
+        <v>-0.06696527063709767</v>
       </c>
       <c r="DH3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.03338266081356252</v>
+        <v>0.1018915075191714</v>
       </c>
       <c r="DJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DK3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL3" t="n">
         <v>0</v>
       </c>
       <c r="DM3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DN3" t="n">
         <v>-0</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.01225312818653543</v>
+        <v>-0.110982135805394</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.006825807843744679</v>
+        <v>-0.03438022738090428</v>
       </c>
       <c r="DQ3" t="n">
         <v>0</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.02299242548621557</v>
+        <v>-0.03977094496444791</v>
       </c>
       <c r="DS3" t="n">
         <v>-0</v>
       </c>
       <c r="DT3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DU3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DV3" t="n">
         <v>-0</v>
@@ -1949,25 +1949,25 @@
         <v>-0</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.04868924310178704</v>
+        <v>0.1985181835095622</v>
       </c>
       <c r="DY3" t="n">
-        <v>-0.001266795595142534</v>
+        <v>0.03228284866044049</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.06467046440704706</v>
+        <v>-0.06464749575176479</v>
       </c>
       <c r="EB3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EC3" t="n">
         <v>0</v>
       </c>
       <c r="ED3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EE3" t="n">
         <v>0</v>
@@ -1976,22 +1976,22 @@
         <v>0</v>
       </c>
       <c r="EG3" t="n">
-        <v>-0.0126626221037563</v>
+        <v>0.193939037691355</v>
       </c>
       <c r="EH3" t="n">
-        <v>-0.03279182127458668</v>
+        <v>0.03258746861298611</v>
       </c>
       <c r="EI3" t="n">
         <v>0</v>
       </c>
       <c r="EJ3" t="n">
-        <v>-0.0299309941353142</v>
+        <v>-0.0198969411325946</v>
       </c>
       <c r="EK3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EM3" t="n">
         <v>0</v>
@@ -2000,55 +2000,55 @@
         <v>0</v>
       </c>
       <c r="EO3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.0785173922031602</v>
+        <v>0.2107061306753051</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.0009158639895149205</v>
+        <v>0.008484049052597127</v>
       </c>
       <c r="ER3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.04381045455516703</v>
+        <v>-0.01655632783822097</v>
       </c>
       <c r="ET3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU3" t="n">
         <v>0</v>
       </c>
       <c r="EV3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EW3" t="n">
         <v>0</v>
       </c>
       <c r="EX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.04778187885878727</v>
+        <v>0.3113152770966436</v>
       </c>
       <c r="EZ3" t="n">
-        <v>-0.02392884313010197</v>
+        <v>-0.06306370752120298</v>
       </c>
       <c r="FA3" t="n">
         <v>0</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.02572340278360696</v>
+        <v>-0.04092066534295249</v>
       </c>
       <c r="FC3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FD3" t="n">
         <v>0</v>
       </c>
       <c r="FE3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF3" t="n">
         <v>0</v>
@@ -2057,43 +2057,43 @@
         <v>0</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.01115603471920129</v>
+        <v>0.03627471065923944</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.03678101973374581</v>
+        <v>0.1704438977011299</v>
       </c>
       <c r="FJ3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.03391888618585637</v>
+        <v>0.07869070660418774</v>
       </c>
       <c r="FL3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN3" t="n">
         <v>0</v>
       </c>
       <c r="FO3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FP3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FQ3" t="n">
-        <v>-0.002889833097161845</v>
+        <v>0.2369033740806112</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.03190669773589752</v>
+        <v>0.03777551187736535</v>
       </c>
       <c r="FS3" t="n">
         <v>0</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.1117485042695526</v>
+        <v>0.04536877489446</v>
       </c>
       <c r="FU3" t="n">
         <v>0</v>
@@ -2105,16 +2105,16 @@
         <v>-0</v>
       </c>
       <c r="FX3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ3" t="n">
-        <v>-0.04943222798155669</v>
+        <v>0.2485716062233331</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.04724634466548371</v>
+        <v>0.08549087921688406</v>
       </c>
       <c r="GB3" t="n">
         <v>0</v>
@@ -2123,16 +2123,16 @@
         <v>-0</v>
       </c>
       <c r="GD3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GE3" t="n">
         <v>0</v>
       </c>
       <c r="GF3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GG3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="4">
@@ -3278,43 +3278,43 @@
         <v>0</v>
       </c>
       <c r="B6" t="n">
-        <v>0.2148940544095548</v>
+        <v>0.1706322721554671</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.0651724944508234</v>
+        <v>-0.0774580442539928</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0124725919741787</v>
+        <v>-0.02714735561220994</v>
       </c>
       <c r="F6" t="n">
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K6" t="n">
-        <v>0.1420327804224374</v>
+        <v>0.1679266368921435</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.07571215726476249</v>
+        <v>-0.1152659858109594</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.01763518332465677</v>
+        <v>-0.06208011504133717</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -3326,112 +3326,112 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>0.08597431350824238</v>
+        <v>0.06051197737764192</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.04453168347676786</v>
+        <v>-0.0570851686111349</v>
       </c>
       <c r="W6" t="n">
-        <v>0.08498691711468485</v>
+        <v>-0.07350421221542247</v>
       </c>
       <c r="X6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
         <v>-0</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA6" t="n">
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.03272929517458844</v>
+        <v>-0.03655705028771327</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.003484357138810761</v>
+        <v>-0.1261765559339477</v>
       </c>
       <c r="AF6" t="n">
-        <v>-0.00344901357034408</v>
+        <v>-0.03291556252642895</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK6" t="n">
         <v>0</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0039530114459862</v>
+        <v>0.07995296180836307</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN6" t="n">
-        <v>-0.05313269415365772</v>
+        <v>-0.08236004832586738</v>
       </c>
       <c r="AO6" t="n">
-        <v>-0.0474487711099817</v>
+        <v>0.06060997651131636</v>
       </c>
       <c r="AP6" t="n">
         <v>0</v>
       </c>
       <c r="AQ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS6" t="n">
         <v>0</v>
       </c>
       <c r="AT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.3675595994477078</v>
+        <v>0.3049761046536439</v>
       </c>
       <c r="AV6" t="n">
         <v>-0</v>
       </c>
       <c r="AW6" t="n">
-        <v>0.001008222074929403</v>
+        <v>-0.07805249471187393</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.08911766705686601</v>
+        <v>-0.1860500214941262</v>
       </c>
       <c r="AY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB6" t="n">
         <v>-0</v>
@@ -3440,25 +3440,25 @@
         <v>0</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0694171297929833</v>
+        <v>-0.02111397884356766</v>
       </c>
       <c r="BE6" t="n">
         <v>0</v>
       </c>
       <c r="BF6" t="n">
-        <v>-0.1469852247639749</v>
+        <v>-0.01863853234484614</v>
       </c>
       <c r="BG6" t="n">
-        <v>-0.08079860074968637</v>
+        <v>0.02218093142041487</v>
       </c>
       <c r="BH6" t="n">
         <v>0</v>
       </c>
       <c r="BI6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK6" t="n">
         <v>0</v>
@@ -3467,16 +3467,16 @@
         <v>-0</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.09907581773735728</v>
+        <v>0.00899288054616286</v>
       </c>
       <c r="BN6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.06732708190704212</v>
+        <v>0.02919001313075084</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.1445133022430088</v>
+        <v>0.04544387291992945</v>
       </c>
       <c r="BQ6" t="n">
         <v>-0</v>
@@ -3488,79 +3488,79 @@
         <v>-0</v>
       </c>
       <c r="BT6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU6" t="n">
         <v>0</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.1584046509045096</v>
+        <v>0.1805286143402956</v>
       </c>
       <c r="BW6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX6" t="n">
-        <v>-0.008345024732231896</v>
+        <v>-0.1455355936505627</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0582206636252055</v>
+        <v>-0.07043385676390049</v>
       </c>
       <c r="BZ6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA6" t="n">
         <v>-0</v>
       </c>
       <c r="CB6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="n">
-        <v>-0.08765631496575296</v>
+        <v>-0.1151811020711924</v>
       </c>
       <c r="CF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.005090969508205863</v>
+        <v>0.09854763273907192</v>
       </c>
       <c r="CH6" t="n">
-        <v>-0.0106762413340965</v>
+        <v>0.01800574148499013</v>
       </c>
       <c r="CI6" t="n">
         <v>-0</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK6" t="n">
         <v>0</v>
       </c>
       <c r="CL6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM6" t="n">
         <v>0</v>
       </c>
       <c r="CN6" t="n">
-        <v>-0.001141363512533369</v>
+        <v>-0.003139651165055325</v>
       </c>
       <c r="CO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP6" t="n">
-        <v>-0.003347267201510092</v>
+        <v>0.007995802482621604</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.003178783385711355</v>
+        <v>-0.001054568944424688</v>
       </c>
       <c r="CR6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS6" t="n">
         <v>-0</v>
@@ -3572,46 +3572,46 @@
         <v>-0</v>
       </c>
       <c r="CV6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW6" t="n">
-        <v>-0.07096771732269931</v>
+        <v>-0.1204220484728549</v>
       </c>
       <c r="CX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.03936630310638888</v>
+        <v>0.1110554108058978</v>
       </c>
       <c r="CZ6" t="n">
-        <v>-0.01448578732309592</v>
+        <v>0.02230967683773214</v>
       </c>
       <c r="DA6" t="n">
         <v>0</v>
       </c>
       <c r="DB6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>-0.01301621469092757</v>
+        <v>-0.05687258987779284</v>
       </c>
       <c r="DG6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.06120930874454412</v>
+        <v>0.01823537408264605</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.009394322036249363</v>
+        <v>-0.101755925909728</v>
       </c>
       <c r="DJ6" t="n">
         <v>-0</v>
@@ -3623,31 +3623,31 @@
         <v>0</v>
       </c>
       <c r="DM6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO6" t="n">
-        <v>-0.06731206922949806</v>
+        <v>-0.05922060794079666</v>
       </c>
       <c r="DP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.00556465801277331</v>
+        <v>-0.003574355053896412</v>
       </c>
       <c r="DR6" t="n">
-        <v>-0.02560719013984462</v>
+        <v>-0.00777536360547073</v>
       </c>
       <c r="DS6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT6" t="n">
         <v>-0</v>
       </c>
       <c r="DU6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV6" t="n">
         <v>0</v>
@@ -3656,52 +3656,52 @@
         <v>-0</v>
       </c>
       <c r="DX6" t="n">
-        <v>-0.0677252070970458</v>
+        <v>-0.032450793432689</v>
       </c>
       <c r="DY6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ6" t="n">
-        <v>-0.02741732346404223</v>
+        <v>0.08283839041964633</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.001811758873684623</v>
+        <v>0.01547908291471798</v>
       </c>
       <c r="EB6" t="n">
         <v>-0</v>
       </c>
       <c r="EC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="ED6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG6" t="n">
-        <v>-0.07415300351938278</v>
+        <v>-0.08099184612984688</v>
       </c>
       <c r="EH6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0207829160270868</v>
+        <v>0.07472913801397289</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.04568408489087549</v>
+        <v>0.03863706937279114</v>
       </c>
       <c r="EK6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN6" t="n">
         <v>-0</v>
@@ -3710,22 +3710,22 @@
         <v>0</v>
       </c>
       <c r="EP6" t="n">
-        <v>-0.02598981795148673</v>
+        <v>-0.04514778788521109</v>
       </c>
       <c r="EQ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.02431261490632297</v>
+        <v>0.07755586924645634</v>
       </c>
       <c r="ES6" t="n">
-        <v>0.02572654835283831</v>
+        <v>-0.005118218837304379</v>
       </c>
       <c r="ET6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV6" t="n">
         <v>0</v>
@@ -3734,19 +3734,19 @@
         <v>-0</v>
       </c>
       <c r="EX6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EY6" t="n">
-        <v>-0.06730556612887298</v>
+        <v>-0.1261031506649398</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.006856869559050609</v>
+        <v>0.1336788874481924</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.001692737190586503</v>
+        <v>0.007226957370423397</v>
       </c>
       <c r="FC6" t="n">
         <v>-0</v>
@@ -3755,25 +3755,25 @@
         <v>0</v>
       </c>
       <c r="FE6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG6" t="n">
         <v>0</v>
       </c>
       <c r="FH6" t="n">
-        <v>-0.04649264147275512</v>
+        <v>0.1050437530697185</v>
       </c>
       <c r="FI6" t="n">
         <v>-0</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.01452933676824529</v>
+        <v>0.0798478297478355</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.01902344654967801</v>
+        <v>0.03598579574605847</v>
       </c>
       <c r="FL6" t="n">
         <v>-0</v>
@@ -3785,28 +3785,28 @@
         <v>-0</v>
       </c>
       <c r="FO6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP6" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ6" t="n">
-        <v>-0.01976446871730043</v>
+        <v>0.0549833394804314</v>
       </c>
       <c r="FR6" t="n">
         <v>0</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.03286796843712864</v>
+        <v>0.1711330612840697</v>
       </c>
       <c r="FT6" t="n">
-        <v>-0.04869569296990808</v>
+        <v>-0.02228286101300066</v>
       </c>
       <c r="FU6" t="n">
         <v>-0</v>
       </c>
       <c r="FV6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW6" t="n">
         <v>0</v>
@@ -3815,22 +3815,22 @@
         <v>0</v>
       </c>
       <c r="FY6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.03917781682246147</v>
+        <v>-0.04799514796080354</v>
       </c>
       <c r="GA6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB6" t="n">
-        <v>-0.08304809158952911</v>
+        <v>0.09029361072465961</v>
       </c>
       <c r="GC6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD6" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE6" t="n">
         <v>-0</v>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
       <c r="B7" t="n">
-        <v>0.06683828911842679</v>
+        <v>0.1687862015222384</v>
       </c>
       <c r="C7" t="n">
         <v>0</v>
@@ -3856,10 +3856,10 @@
         <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.02273766107103135</v>
+        <v>-0.02483144452375674</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.02425491315148753</v>
+        <v>-0.09118729117724571</v>
       </c>
       <c r="G7" t="n">
         <v>-0</v>
@@ -3868,13 +3868,13 @@
         <v>-0</v>
       </c>
       <c r="I7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05121846351366165</v>
+        <v>0.2059326296414792</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -3883,64 +3883,64 @@
         <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.02101595613811584</v>
+        <v>-0.07965246039150856</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.02276778103160125</v>
+        <v>-0.09102367469826754</v>
       </c>
       <c r="P7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T7" t="n">
-        <v>0.01633431150023209</v>
+        <v>0.0906032314011575</v>
       </c>
       <c r="U7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
         <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.01055208517117251</v>
+        <v>-0.08411706499351884</v>
       </c>
       <c r="X7" t="n">
-        <v>0.01254536051030162</v>
+        <v>-0.021470316846743</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA7" t="n">
         <v>0</v>
       </c>
       <c r="AB7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.004121784644244086</v>
+        <v>-0.002701315661671769</v>
       </c>
       <c r="AD7" t="n">
         <v>-0</v>
       </c>
       <c r="AE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.009124635463044787</v>
+        <v>-0.1798669863326122</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.003665884380847915</v>
+        <v>0.009624761342570315</v>
       </c>
       <c r="AH7" t="n">
         <v>-0</v>
@@ -3949,40 +3949,40 @@
         <v>-0</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK7" t="n">
         <v>0</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.008092224686457605</v>
+        <v>0.07032471319908359</v>
       </c>
       <c r="AM7" t="n">
         <v>-0</v>
       </c>
       <c r="AN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO7" t="n">
-        <v>-0.01918069407562068</v>
+        <v>-0.01135033640896774</v>
       </c>
       <c r="AP7" t="n">
-        <v>-0.0129942416549228</v>
+        <v>-0.02987327465182414</v>
       </c>
       <c r="AQ7" t="n">
         <v>-0</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
       </c>
       <c r="AT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.0971539332918098</v>
+        <v>0.3777475559675858</v>
       </c>
       <c r="AV7" t="n">
         <v>-0</v>
@@ -3991,10 +3991,10 @@
         <v>0</v>
       </c>
       <c r="AX7" t="n">
-        <v>-0.008808726209790011</v>
+        <v>-0.2154916377064754</v>
       </c>
       <c r="AY7" t="n">
-        <v>-0.01836468545159951</v>
+        <v>-0.1227230609708017</v>
       </c>
       <c r="AZ7" t="n">
         <v>-0</v>
@@ -4009,7 +4009,7 @@
         <v>0</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.02637494937591453</v>
+        <v>-0.01378249597728389</v>
       </c>
       <c r="BE7" t="n">
         <v>0</v>
@@ -4018,16 +4018,16 @@
         <v>0</v>
       </c>
       <c r="BG7" t="n">
-        <v>-0.0615331784058313</v>
+        <v>-0.02005243170381951</v>
       </c>
       <c r="BH7" t="n">
-        <v>-0.04881952876082857</v>
+        <v>-0.09117730556502296</v>
       </c>
       <c r="BI7" t="n">
         <v>0</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK7" t="n">
         <v>0</v>
@@ -4036,7 +4036,7 @@
         <v>0</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.03505589985416163</v>
+        <v>0.04963994899173043</v>
       </c>
       <c r="BN7" t="n">
         <v>-0</v>
@@ -4045,37 +4045,37 @@
         <v>-0</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.02054332387517647</v>
+        <v>0.08870358436176043</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.02155182616029998</v>
+        <v>0.0454975082688724</v>
       </c>
       <c r="BR7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.04180182571539127</v>
+        <v>0.2260220128116578</v>
       </c>
       <c r="BW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX7" t="n">
         <v>0</v>
       </c>
       <c r="BY7" t="n">
-        <v>-0.01552320983918893</v>
+        <v>-0.06041932784548697</v>
       </c>
       <c r="BZ7" t="n">
-        <v>-0.002857280452661095</v>
+        <v>-0.1328535612566051</v>
       </c>
       <c r="CA7" t="n">
         <v>-0</v>
@@ -4084,187 +4084,187 @@
         <v>-0</v>
       </c>
       <c r="CC7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE7" t="n">
-        <v>-0.02185431416917163</v>
+        <v>-0.09818954355945478</v>
       </c>
       <c r="CF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG7" t="n">
         <v>-0</v>
       </c>
       <c r="CH7" t="n">
-        <v>0.0007882613757868945</v>
+        <v>0.02437833153381812</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.01739835042109649</v>
+        <v>0.09091177247992854</v>
       </c>
       <c r="CJ7" t="n">
         <v>0</v>
       </c>
       <c r="CK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL7" t="n">
         <v>0</v>
       </c>
       <c r="CM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0005574651877753846</v>
+        <v>-0.01544805639570631</v>
       </c>
       <c r="CO7" t="n">
         <v>-0</v>
       </c>
       <c r="CP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0003680763633037602</v>
+        <v>0.004895661737043317</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0007470704001217782</v>
+        <v>-0.003201895504655938</v>
       </c>
       <c r="CS7" t="n">
         <v>-0</v>
       </c>
       <c r="CT7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW7" t="n">
-        <v>-0.01531424525833571</v>
+        <v>-0.09819966610837874</v>
       </c>
       <c r="CX7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY7" t="n">
         <v>0</v>
       </c>
       <c r="CZ7" t="n">
-        <v>0.003706337431959918</v>
+        <v>0.02104981586622067</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.01872135504987369</v>
+        <v>0.1069237015676148</v>
       </c>
       <c r="DB7" t="n">
         <v>0</v>
       </c>
       <c r="DC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DF7" t="n">
-        <v>-0.01376528015335258</v>
+        <v>-0.03948800977892965</v>
       </c>
       <c r="DG7" t="n">
         <v>0</v>
       </c>
       <c r="DH7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.02368097293992542</v>
+        <v>-0.0453430784457429</v>
       </c>
       <c r="DJ7" t="n">
-        <v>-0.001044540808603807</v>
+        <v>0.03167957590708106</v>
       </c>
       <c r="DK7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN7" t="n">
         <v>-0</v>
       </c>
       <c r="DO7" t="n">
-        <v>-0.004005123600715156</v>
+        <v>-0.02459904734968323</v>
       </c>
       <c r="DP7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ7" t="n">
         <v>0</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.01784323491443598</v>
+        <v>-0.05385923890359594</v>
       </c>
       <c r="DS7" t="n">
-        <v>-0.007394951304354211</v>
+        <v>-0.01380851206993531</v>
       </c>
       <c r="DT7" t="n">
         <v>-0</v>
       </c>
       <c r="DU7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX7" t="n">
-        <v>-0.03386893442787201</v>
+        <v>-0.06889617642321973</v>
       </c>
       <c r="DY7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.01791466953574379</v>
+        <v>0.0245461319786223</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.01358498748725337</v>
+        <v>0.07831460968708211</v>
       </c>
       <c r="EC7" t="n">
         <v>-0</v>
       </c>
       <c r="ED7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG7" t="n">
-        <v>-0.0204647742873071</v>
+        <v>-0.02345475312887155</v>
       </c>
       <c r="EH7" t="n">
         <v>-0</v>
       </c>
       <c r="EI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EJ7" t="n">
-        <v>0.003098217425834757</v>
+        <v>-0.002927122415376774</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.01448990289364832</v>
+        <v>0.03490127061564949</v>
       </c>
       <c r="EL7" t="n">
         <v>0</v>
@@ -4273,25 +4273,25 @@
         <v>-0</v>
       </c>
       <c r="EN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP7" t="n">
-        <v>-0.009812493303619439</v>
+        <v>-0.01610328396784396</v>
       </c>
       <c r="EQ7" t="n">
         <v>-0</v>
       </c>
       <c r="ER7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.006794212969962391</v>
+        <v>-0.03737300119690488</v>
       </c>
       <c r="ET7" t="n">
-        <v>-0.001479928696325481</v>
+        <v>0.07540896203812122</v>
       </c>
       <c r="EU7" t="n">
         <v>0</v>
@@ -4300,13 +4300,13 @@
         <v>0</v>
       </c>
       <c r="EW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY7" t="n">
-        <v>-0.01546926730086737</v>
+        <v>-0.114784887764586</v>
       </c>
       <c r="EZ7" t="n">
         <v>-0</v>
@@ -4315,16 +4315,16 @@
         <v>-0</v>
       </c>
       <c r="FB7" t="n">
-        <v>0.005903259287382938</v>
+        <v>0.005188947530464382</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.02302554659989057</v>
+        <v>0.0842392826127405</v>
       </c>
       <c r="FD7" t="n">
         <v>0</v>
       </c>
       <c r="FE7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF7" t="n">
         <v>-0</v>
@@ -4333,25 +4333,25 @@
         <v>0</v>
       </c>
       <c r="FH7" t="n">
-        <v>-0.02049137052293495</v>
+        <v>0.1233139586439599</v>
       </c>
       <c r="FI7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ7" t="n">
         <v>-0</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.01662596139332302</v>
+        <v>-0.0833181953088164</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.01165572835126054</v>
+        <v>0.07523287181865397</v>
       </c>
       <c r="FM7" t="n">
         <v>0</v>
       </c>
       <c r="FN7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO7" t="n">
         <v>0</v>
@@ -4360,7 +4360,7 @@
         <v>0</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.003515255631533317</v>
+        <v>0.03623691624551852</v>
       </c>
       <c r="FR7" t="n">
         <v>0</v>
@@ -4369,37 +4369,37 @@
         <v>-0</v>
       </c>
       <c r="FT7" t="n">
-        <v>-0.01991128506145687</v>
+        <v>-0.06333117122800153</v>
       </c>
       <c r="FU7" t="n">
-        <v>0.005038631712644738</v>
+        <v>-0.01073768528026246</v>
       </c>
       <c r="FV7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.002474377831257899</v>
+        <v>-0.02413355664964482</v>
       </c>
       <c r="GA7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB7" t="n">
         <v>-0</v>
       </c>
       <c r="GC7" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD7" t="n">
-        <v>-0.01554495380139698</v>
+        <v>0.08974863378365489</v>
       </c>
       <c r="GE7" t="n">
         <v>0</v>
@@ -4408,7 +4408,7 @@
         <v>-0</v>
       </c>
       <c r="GG7" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -4416,43 +4416,43 @@
         <v>0</v>
       </c>
       <c r="B8" t="n">
-        <v>0.2648990402019546</v>
+        <v>0.2353733376436543</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.06364140287672218</v>
+        <v>-0.07839306342329959</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.07191386436743992</v>
+        <v>-0.05410155477906965</v>
       </c>
       <c r="F8" t="n">
         <v>0</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>0.1882078033791055</v>
+        <v>0.2608273046357167</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.05873128424689916</v>
+        <v>-0.1059848238929392</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.05330417648261011</v>
+        <v>-0.1164737847705808</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -4470,70 +4470,70 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0.09416760408445721</v>
+        <v>0.05720382977004805</v>
       </c>
       <c r="U8" t="n">
         <v>-0</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.03030098059636517</v>
+        <v>-0.03741424251598174</v>
       </c>
       <c r="W8" t="n">
-        <v>0.07758638818348287</v>
+        <v>-0.08940073064772508</v>
       </c>
       <c r="X8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
         <v>-0</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA8" t="n">
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC8" t="n">
-        <v>0.04987567131224008</v>
+        <v>-0.009850201850078582</v>
       </c>
       <c r="AD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>-0.002097180299950283</v>
+        <v>-0.1542226209465578</v>
       </c>
       <c r="AF8" t="n">
-        <v>-0.01740236260162581</v>
+        <v>-0.03310049458222812</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK8" t="n">
         <v>0</v>
       </c>
       <c r="AL8" t="n">
-        <v>0.02270983974400179</v>
+        <v>0.08712679014222223</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AN8" t="n">
-        <v>-0.04960505299730634</v>
+        <v>-0.08084813143826346</v>
       </c>
       <c r="AO8" t="n">
-        <v>-0.04994810900760096</v>
+        <v>0.06524094769591551</v>
       </c>
       <c r="AP8" t="n">
         <v>0</v>
@@ -4542,34 +4542,34 @@
         <v>-0</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
       </c>
       <c r="AT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.3905040067708478</v>
+        <v>0.306664441190324</v>
       </c>
       <c r="AV8" t="n">
         <v>-0</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.03200977409363412</v>
+        <v>-0.06810446301145984</v>
       </c>
       <c r="AX8" t="n">
-        <v>0.0493912438032896</v>
+        <v>-0.281191273191148</v>
       </c>
       <c r="AY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB8" t="n">
         <v>-0</v>
@@ -4578,25 +4578,25 @@
         <v>0</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.03988463035960109</v>
+        <v>0.005146985323950722</v>
       </c>
       <c r="BE8" t="n">
         <v>0</v>
       </c>
       <c r="BF8" t="n">
-        <v>-0.1215189061153849</v>
+        <v>-0.04476469417758509</v>
       </c>
       <c r="BG8" t="n">
-        <v>-0.1269709545573439</v>
+        <v>0.02412687044939064</v>
       </c>
       <c r="BH8" t="n">
         <v>0</v>
       </c>
       <c r="BI8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK8" t="n">
         <v>0</v>
@@ -4605,16 +4605,16 @@
         <v>-0</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.09065388094274644</v>
+        <v>0.01106427292644956</v>
       </c>
       <c r="BN8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.07141483016566899</v>
+        <v>0.04202506853227025</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.125689751849911</v>
+        <v>0.08003671207005704</v>
       </c>
       <c r="BQ8" t="n">
         <v>-0</v>
@@ -4626,103 +4626,103 @@
         <v>-0</v>
       </c>
       <c r="BT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU8" t="n">
         <v>0</v>
       </c>
       <c r="BV8" t="n">
-        <v>0.1840998620786753</v>
+        <v>0.1785631405404526</v>
       </c>
       <c r="BW8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX8" t="n">
-        <v>0.007373315317651106</v>
+        <v>-0.09953485935749436</v>
       </c>
       <c r="BY8" t="n">
-        <v>0.03533067888082586</v>
+        <v>-0.104567444291339</v>
       </c>
       <c r="BZ8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA8" t="n">
         <v>-0</v>
       </c>
       <c r="CB8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="n">
         <v>-0</v>
       </c>
       <c r="CE8" t="n">
-        <v>-0.09411233440386485</v>
+        <v>-0.1285523780849968</v>
       </c>
       <c r="CF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG8" t="n">
-        <v>-0.009635503310069224</v>
+        <v>0.1013578965095372</v>
       </c>
       <c r="CH8" t="n">
-        <v>0.001782539740064834</v>
+        <v>0.03547011606662907</v>
       </c>
       <c r="CI8" t="n">
         <v>-0</v>
       </c>
       <c r="CJ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CK8" t="n">
         <v>0</v>
       </c>
       <c r="CL8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM8" t="n">
         <v>0</v>
       </c>
       <c r="CN8" t="n">
-        <v>-0.001409433437527285</v>
+        <v>-0.01387260307236169</v>
       </c>
       <c r="CO8" t="n">
         <v>-0</v>
       </c>
       <c r="CP8" t="n">
-        <v>-0.004627204655871276</v>
+        <v>0.008985469591184719</v>
       </c>
       <c r="CQ8" t="n">
-        <v>-0.01135369257396618</v>
+        <v>0.007211084745504209</v>
       </c>
       <c r="CR8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU8" t="n">
         <v>-0</v>
       </c>
       <c r="CV8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW8" t="n">
-        <v>-0.06396327989885699</v>
+        <v>-0.1301223562474862</v>
       </c>
       <c r="CX8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY8" t="n">
-        <v>0.02656051621945607</v>
+        <v>0.1162462718324239</v>
       </c>
       <c r="CZ8" t="n">
-        <v>-0.006136689187345907</v>
+        <v>0.04338081676072716</v>
       </c>
       <c r="DA8" t="n">
         <v>0</v>
@@ -4734,22 +4734,22 @@
         <v>-0</v>
       </c>
       <c r="DD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE8" t="n">
         <v>0</v>
       </c>
       <c r="DF8" t="n">
-        <v>-0.02181945762226763</v>
+        <v>-0.07622799695936343</v>
       </c>
       <c r="DG8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH8" t="n">
-        <v>0.05355042462501344</v>
+        <v>3.919477699518364e-05</v>
       </c>
       <c r="DI8" t="n">
-        <v>0.01858087002203559</v>
+        <v>-0.03954791720084396</v>
       </c>
       <c r="DJ8" t="n">
         <v>-0</v>
@@ -4761,25 +4761,25 @@
         <v>0</v>
       </c>
       <c r="DM8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO8" t="n">
-        <v>-0.07663346248126031</v>
+        <v>-0.06080687601075513</v>
       </c>
       <c r="DP8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ8" t="n">
-        <v>-0.0112058557372158</v>
+        <v>-0.04532146169758358</v>
       </c>
       <c r="DR8" t="n">
-        <v>-0.04961405090530052</v>
+        <v>-0.06195085424856996</v>
       </c>
       <c r="DS8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT8" t="n">
         <v>-0</v>
@@ -4794,16 +4794,16 @@
         <v>-0</v>
       </c>
       <c r="DX8" t="n">
-        <v>-0.0381966733278794</v>
+        <v>-0.01717343853746612</v>
       </c>
       <c r="DY8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ8" t="n">
-        <v>-0.03334485551282911</v>
+        <v>0.05802297107308238</v>
       </c>
       <c r="EA8" t="n">
-        <v>-0.01026238319736849</v>
+        <v>0.01744525374124641</v>
       </c>
       <c r="EB8" t="n">
         <v>-0</v>
@@ -4812,58 +4812,58 @@
         <v>-0</v>
       </c>
       <c r="ED8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG8" t="n">
-        <v>-0.07990268657284076</v>
+        <v>-0.0763522474910381</v>
       </c>
       <c r="EH8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI8" t="n">
-        <v>0.001161588539049069</v>
+        <v>0.06788308337701915</v>
       </c>
       <c r="EJ8" t="n">
-        <v>0.0748266662404817</v>
+        <v>0.04547308995557858</v>
       </c>
       <c r="EK8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EL8" t="n">
         <v>-0</v>
       </c>
       <c r="EM8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN8" t="n">
         <v>-0</v>
       </c>
       <c r="EO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP8" t="n">
-        <v>-0.0169718920761699</v>
+        <v>-0.05342877962211792</v>
       </c>
       <c r="EQ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER8" t="n">
-        <v>0.01041668589203739</v>
+        <v>0.04467815189276288</v>
       </c>
       <c r="ES8" t="n">
-        <v>0.03681348732720119</v>
+        <v>0.02239270911970695</v>
       </c>
       <c r="ET8" t="n">
         <v>-0</v>
       </c>
       <c r="EU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV8" t="n">
         <v>0</v>
@@ -4875,16 +4875,16 @@
         <v>-0</v>
       </c>
       <c r="EY8" t="n">
-        <v>-0.06400992899520146</v>
+        <v>-0.1383653601905873</v>
       </c>
       <c r="EZ8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA8" t="n">
-        <v>0.0006485136987018916</v>
+        <v>0.1354009370328877</v>
       </c>
       <c r="FB8" t="n">
-        <v>0.01428090165400867</v>
+        <v>0.019277715881436</v>
       </c>
       <c r="FC8" t="n">
         <v>-0</v>
@@ -4893,25 +4893,25 @@
         <v>0</v>
       </c>
       <c r="FE8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG8" t="n">
         <v>0</v>
       </c>
       <c r="FH8" t="n">
-        <v>-0.02880828116802735</v>
+        <v>0.1408027850236236</v>
       </c>
       <c r="FI8" t="n">
         <v>-0</v>
       </c>
       <c r="FJ8" t="n">
-        <v>0.009921336993986994</v>
+        <v>0.1013492326910454</v>
       </c>
       <c r="FK8" t="n">
-        <v>-0.006691200379684304</v>
+        <v>-0.01139569152545456</v>
       </c>
       <c r="FL8" t="n">
         <v>-0</v>
@@ -4920,31 +4920,31 @@
         <v>0</v>
       </c>
       <c r="FN8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO8" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP8" t="n">
         <v>-0</v>
       </c>
       <c r="FQ8" t="n">
-        <v>-0.04084474282386334</v>
+        <v>0.04232392245484752</v>
       </c>
       <c r="FR8" t="n">
         <v>0</v>
       </c>
       <c r="FS8" t="n">
-        <v>0.02779985044900109</v>
+        <v>0.1902671003464372</v>
       </c>
       <c r="FT8" t="n">
-        <v>-0.06537713071189176</v>
+        <v>-0.04474993646762199</v>
       </c>
       <c r="FU8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW8" t="n">
         <v>0</v>
@@ -4953,22 +4953,22 @@
         <v>0</v>
       </c>
       <c r="FY8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ8" t="n">
-        <v>0.05256130193450508</v>
+        <v>-0.0465041459334345</v>
       </c>
       <c r="GA8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB8" t="n">
-        <v>-0.05220353247274824</v>
+        <v>0.04148127618042176</v>
       </c>
       <c r="GC8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GD8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE8" t="n">
         <v>-0</v>
@@ -4977,15 +4977,15 @@
         <v>0</v>
       </c>
       <c r="GG8" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B9" t="n">
-        <v>0.1410202782558627</v>
+        <v>0.2015087882827337</v>
       </c>
       <c r="C9" t="n">
         <v>0</v>
@@ -4994,10 +4994,10 @@
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.02579296822356879</v>
+        <v>0.008832671389168937</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.07882343671008296</v>
+        <v>-0.1571838707134219</v>
       </c>
       <c r="G9" t="n">
         <v>-0</v>
@@ -5009,10 +5009,10 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1149352144948177</v>
+        <v>0.2557232805764192</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -5021,64 +5021,64 @@
         <v>0</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.00560216294862142</v>
+        <v>-0.07619773662051622</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.06349529566387704</v>
+        <v>-0.167138383790765</v>
       </c>
       <c r="P9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
         <v>-0</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T9" t="n">
-        <v>0.02486221085034998</v>
+        <v>0.09524881074351432</v>
       </c>
       <c r="U9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
         <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.03882555453073414</v>
+        <v>-0.05359710639944983</v>
       </c>
       <c r="X9" t="n">
-        <v>0.007953206099217533</v>
+        <v>-0.06703665597682279</v>
       </c>
       <c r="Y9" t="n">
         <v>-0</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB9" t="n">
         <v>-0</v>
       </c>
       <c r="AC9" t="n">
-        <v>-0.00366154530372284</v>
+        <v>-0.03479815546073088</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.01030698646265549</v>
+        <v>-0.1635822108018739</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.01104328905903841</v>
+        <v>0.06093839468582308</v>
       </c>
       <c r="AH9" t="n">
         <v>0</v>
@@ -5093,22 +5093,22 @@
         <v>0</v>
       </c>
       <c r="AL9" t="n">
-        <v>0.0285425844770852</v>
+        <v>0.1136816662555732</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO9" t="n">
-        <v>-0.005938713057855526</v>
+        <v>-0.003892202149601039</v>
       </c>
       <c r="AP9" t="n">
-        <v>-0.04392575069612908</v>
+        <v>-0.07351692288668184</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR9" t="n">
         <v>-0</v>
@@ -5120,34 +5120,34 @@
         <v>-0</v>
       </c>
       <c r="AU9" t="n">
-        <v>0.1481300511189013</v>
+        <v>0.4866222743713132</v>
       </c>
       <c r="AV9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW9" t="n">
         <v>0</v>
       </c>
       <c r="AX9" t="n">
-        <v>-0.05168577225969324</v>
+        <v>-0.204528775342306</v>
       </c>
       <c r="AY9" t="n">
-        <v>-0.08266090042861632</v>
+        <v>-0.1761005830301949</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC9" t="n">
         <v>0</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.06111238188573443</v>
+        <v>-0.09960983888230406</v>
       </c>
       <c r="BE9" t="n">
         <v>0</v>
@@ -5156,52 +5156,52 @@
         <v>0</v>
       </c>
       <c r="BG9" t="n">
-        <v>-0.0278838993387512</v>
+        <v>-0.007527455116034876</v>
       </c>
       <c r="BH9" t="n">
-        <v>-0.05938349331437833</v>
+        <v>-0.0562948849992443</v>
       </c>
       <c r="BI9" t="n">
         <v>0</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.05561734711797324</v>
+        <v>0.08703974442836956</v>
       </c>
       <c r="BN9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.02511140931994077</v>
+        <v>0.01816003836746756</v>
       </c>
       <c r="BQ9" t="n">
-        <v>0.01270509173770959</v>
+        <v>0.05698631590581078</v>
       </c>
       <c r="BR9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS9" t="n">
         <v>0</v>
       </c>
       <c r="BT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV9" t="n">
-        <v>0.08232317751242886</v>
+        <v>0.2897646828099211</v>
       </c>
       <c r="BW9" t="n">
         <v>0</v>
@@ -5210,91 +5210,91 @@
         <v>0</v>
       </c>
       <c r="BY9" t="n">
-        <v>-0.03309360632430882</v>
+        <v>-0.06714537670102694</v>
       </c>
       <c r="BZ9" t="n">
-        <v>-0.03097297870566606</v>
+        <v>-0.1671925799586078</v>
       </c>
       <c r="CA9" t="n">
         <v>-0</v>
       </c>
       <c r="CB9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD9" t="n">
         <v>-0</v>
       </c>
       <c r="CE9" t="n">
-        <v>-0.03833787590266918</v>
+        <v>-0.1265656175447178</v>
       </c>
       <c r="CF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG9" t="n">
         <v>-0</v>
       </c>
       <c r="CH9" t="n">
-        <v>-0.004987176429769227</v>
+        <v>0.02860946101413292</v>
       </c>
       <c r="CI9" t="n">
-        <v>0.03977461585273488</v>
+        <v>0.08505544410677045</v>
       </c>
       <c r="CJ9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK9" t="n">
         <v>0</v>
       </c>
       <c r="CL9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM9" t="n">
         <v>0</v>
       </c>
       <c r="CN9" t="n">
-        <v>-0.001049258113982049</v>
+        <v>-0.04694086833253814</v>
       </c>
       <c r="CO9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ9" t="n">
-        <v>0.001416367136546059</v>
+        <v>0.03293719970098148</v>
       </c>
       <c r="CR9" t="n">
-        <v>-0.001635803509596689</v>
+        <v>-0.001066267819364123</v>
       </c>
       <c r="CS9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV9" t="n">
         <v>-0</v>
       </c>
       <c r="CW9" t="n">
-        <v>-0.03423707695073189</v>
+        <v>-0.1182827976514623</v>
       </c>
       <c r="CX9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY9" t="n">
         <v>0</v>
       </c>
       <c r="CZ9" t="n">
-        <v>-0.002506715589714907</v>
+        <v>0.01667061625584979</v>
       </c>
       <c r="DA9" t="n">
-        <v>0.04461884527778701</v>
+        <v>0.1054798521902325</v>
       </c>
       <c r="DB9" t="n">
         <v>0</v>
@@ -5303,13 +5303,13 @@
         <v>-0</v>
       </c>
       <c r="DD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE9" t="n">
         <v>0</v>
       </c>
       <c r="DF9" t="n">
-        <v>-0.05052523770300458</v>
+        <v>-0.101308693983745</v>
       </c>
       <c r="DG9" t="n">
         <v>0</v>
@@ -5318,25 +5318,25 @@
         <v>-0</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.0548247292459323</v>
+        <v>-0.03277410078996038</v>
       </c>
       <c r="DJ9" t="n">
-        <v>0.0008467604903610016</v>
+        <v>0.0286565067489722</v>
       </c>
       <c r="DK9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL9" t="n">
         <v>0</v>
       </c>
       <c r="DM9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN9" t="n">
         <v>-0</v>
       </c>
       <c r="DO9" t="n">
-        <v>-0.01960381105687268</v>
+        <v>-0.1062684540659365</v>
       </c>
       <c r="DP9" t="n">
         <v>0</v>
@@ -5345,67 +5345,67 @@
         <v>0</v>
       </c>
       <c r="DR9" t="n">
-        <v>0.02044551779355115</v>
+        <v>0.02997968440331831</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.005302105553416011</v>
+        <v>0.1573936511732467</v>
       </c>
       <c r="DT9" t="n">
         <v>-0</v>
       </c>
       <c r="DU9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV9" t="n">
         <v>0</v>
       </c>
       <c r="DW9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX9" t="n">
-        <v>-0.04419225231264957</v>
+        <v>-0.05833062817400143</v>
       </c>
       <c r="DY9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA9" t="n">
-        <v>0.01743247987512856</v>
+        <v>0.0918020030027885</v>
       </c>
       <c r="EB9" t="n">
-        <v>0.02563456933576336</v>
+        <v>0.01708952510682664</v>
       </c>
       <c r="EC9" t="n">
         <v>-0</v>
       </c>
       <c r="ED9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF9" t="n">
         <v>0</v>
       </c>
       <c r="EG9" t="n">
-        <v>-0.03038991310809848</v>
+        <v>-0.04081412368330629</v>
       </c>
       <c r="EH9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ9" t="n">
-        <v>0.007778460140320567</v>
+        <v>-0.03964954511134561</v>
       </c>
       <c r="EK9" t="n">
-        <v>0.04018846782319158</v>
+        <v>0.02599058868087734</v>
       </c>
       <c r="EL9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM9" t="n">
         <v>-0</v>
@@ -5417,22 +5417,22 @@
         <v>0</v>
       </c>
       <c r="EP9" t="n">
-        <v>-0.02687275141575664</v>
+        <v>-0.0318284881283607</v>
       </c>
       <c r="EQ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER9" t="n">
         <v>-0</v>
       </c>
       <c r="ES9" t="n">
-        <v>-0.01632540345980725</v>
+        <v>-0.1087098938771099</v>
       </c>
       <c r="ET9" t="n">
-        <v>-0.005577923106071601</v>
+        <v>0.0267020106284029</v>
       </c>
       <c r="EU9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV9" t="n">
         <v>0</v>
@@ -5444,34 +5444,34 @@
         <v>0</v>
       </c>
       <c r="EY9" t="n">
-        <v>-0.0346001036596696</v>
+        <v>-0.1340047200148723</v>
       </c>
       <c r="EZ9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA9" t="n">
         <v>-0</v>
       </c>
       <c r="FB9" t="n">
-        <v>-0.0002240284847396851</v>
+        <v>0.001492719765589038</v>
       </c>
       <c r="FC9" t="n">
-        <v>0.04413143916719909</v>
+        <v>0.101721222699002</v>
       </c>
       <c r="FD9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE9" t="n">
         <v>0</v>
       </c>
       <c r="FF9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG9" t="n">
         <v>0</v>
       </c>
       <c r="FH9" t="n">
-        <v>-0.02344656844886248</v>
+        <v>0.07580462755230376</v>
       </c>
       <c r="FI9" t="n">
         <v>0</v>
@@ -5480,64 +5480,64 @@
         <v>-0</v>
       </c>
       <c r="FK9" t="n">
-        <v>0.009773127294445251</v>
+        <v>-0.0147669447743872</v>
       </c>
       <c r="FL9" t="n">
-        <v>0.03340830886636971</v>
+        <v>0.1068929183547704</v>
       </c>
       <c r="FM9" t="n">
         <v>0</v>
       </c>
       <c r="FN9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO9" t="n">
         <v>0</v>
       </c>
       <c r="FP9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ9" t="n">
-        <v>-0.006505755616033635</v>
+        <v>0.05707066229066221</v>
       </c>
       <c r="FR9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FS9" t="n">
         <v>-0</v>
       </c>
       <c r="FT9" t="n">
-        <v>-0.0325039344304392</v>
+        <v>-0.05570597652873685</v>
       </c>
       <c r="FU9" t="n">
-        <v>0.02686016396421205</v>
+        <v>-0.02088249057128386</v>
       </c>
       <c r="FV9" t="n">
         <v>-0</v>
       </c>
       <c r="FW9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ9" t="n">
-        <v>0.0007681062586894554</v>
+        <v>-0.01771087548876747</v>
       </c>
       <c r="GA9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB9" t="n">
         <v>-0</v>
       </c>
       <c r="GC9" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD9" t="n">
-        <v>-0.01861151155108751</v>
+        <v>0.1148247918943325</v>
       </c>
       <c r="GE9" t="n">
         <v>-0</v>
@@ -5546,7 +5546,7 @@
         <v>-0</v>
       </c>
       <c r="GG9" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -5554,7 +5554,7 @@
         <v>0</v>
       </c>
       <c r="B10" t="n">
-        <v>0.105393607392874</v>
+        <v>0.2832275625025632</v>
       </c>
       <c r="C10" t="n">
         <v>0</v>
@@ -5563,13 +5563,13 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.03862591179466556</v>
+        <v>-0.04008643136300927</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.06662024249647405</v>
+        <v>-0.1882951302530481</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H10" t="n">
         <v>-0</v>
@@ -5578,10 +5578,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K10" t="n">
-        <v>0.09218639070948313</v>
+        <v>0.3762457073836938</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -5590,64 +5590,64 @@
         <v>0</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.02775152064041153</v>
+        <v>-0.1569937078462069</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.04207145342588373</v>
+        <v>-0.1496243211913337</v>
       </c>
       <c r="P10" t="n">
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T10" t="n">
-        <v>0.01197178530850308</v>
+        <v>0.1246878288380968</v>
       </c>
       <c r="U10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
       <c r="W10" t="n">
-        <v>-0.01364792404645785</v>
+        <v>-0.127595063672073</v>
       </c>
       <c r="X10" t="n">
-        <v>0.01455155825535077</v>
+        <v>-0.01436556341489707</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
       </c>
       <c r="AB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>-0.002242225910422958</v>
+        <v>-0.01746676404911722</v>
       </c>
       <c r="AD10" t="n">
         <v>-0</v>
       </c>
       <c r="AE10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.007627847054635488</v>
+        <v>-0.2485127230839589</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.006208549645664025</v>
+        <v>0.03032806732741581</v>
       </c>
       <c r="AH10" t="n">
         <v>-0</v>
@@ -5662,7 +5662,7 @@
         <v>0</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.008324544445089087</v>
+        <v>0.06610935668407214</v>
       </c>
       <c r="AM10" t="n">
         <v>-0</v>
@@ -5671,10 +5671,10 @@
         <v>0</v>
       </c>
       <c r="AO10" t="n">
-        <v>-0.01568531989472562</v>
+        <v>-0.03835706685208139</v>
       </c>
       <c r="AP10" t="n">
-        <v>-0.01436509116944706</v>
+        <v>-0.02136791280577623</v>
       </c>
       <c r="AQ10" t="n">
         <v>-0</v>
@@ -5689,7 +5689,7 @@
         <v>0</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.1091754340393463</v>
+        <v>0.5179461084391882</v>
       </c>
       <c r="AV10" t="n">
         <v>-0</v>
@@ -5698,25 +5698,25 @@
         <v>0</v>
       </c>
       <c r="AX10" t="n">
-        <v>-0.03669851705789688</v>
+        <v>-0.2942258899239366</v>
       </c>
       <c r="AY10" t="n">
-        <v>-0.05013403933667113</v>
+        <v>-0.2054961001066058</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA10" t="n">
         <v>-0</v>
       </c>
       <c r="BB10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BC10" t="n">
         <v>0</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.03930204194752713</v>
+        <v>-0.05036479468796659</v>
       </c>
       <c r="BE10" t="n">
         <v>0</v>
@@ -5725,25 +5725,25 @@
         <v>0</v>
       </c>
       <c r="BG10" t="n">
-        <v>-0.06080138089730613</v>
+        <v>-0.01670522631010368</v>
       </c>
       <c r="BH10" t="n">
-        <v>-0.05735288126050353</v>
+        <v>-0.110889799295056</v>
       </c>
       <c r="BI10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK10" t="n">
         <v>0</v>
       </c>
       <c r="BL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.03933351222411553</v>
+        <v>0.0687648575546926</v>
       </c>
       <c r="BN10" t="n">
         <v>-0</v>
@@ -5752,13 +5752,13 @@
         <v>-0</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.02841351658683119</v>
+        <v>0.1045698354027385</v>
       </c>
       <c r="BQ10" t="n">
-        <v>0.01779833351607879</v>
+        <v>0.05569350922896975</v>
       </c>
       <c r="BR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="n">
         <v>-0</v>
@@ -5767,10 +5767,10 @@
         <v>0</v>
       </c>
       <c r="BU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.05414113951792002</v>
+        <v>0.3029787903547357</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
@@ -5779,10 +5779,10 @@
         <v>0</v>
       </c>
       <c r="BY10" t="n">
-        <v>-0.01566437857453054</v>
+        <v>-0.09145820274915895</v>
       </c>
       <c r="BZ10" t="n">
-        <v>-0.01197632225145324</v>
+        <v>-0.106989416912537</v>
       </c>
       <c r="CA10" t="n">
         <v>-0</v>
@@ -5791,148 +5791,148 @@
         <v>-0</v>
       </c>
       <c r="CC10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE10" t="n">
-        <v>-0.02764364976824194</v>
+        <v>-0.1310496851615393</v>
       </c>
       <c r="CF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG10" t="n">
         <v>-0</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.002673894631209749</v>
+        <v>0.03525727402622833</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.02650585125103443</v>
+        <v>0.1008776312480682</v>
       </c>
       <c r="CJ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL10" t="n">
         <v>0</v>
       </c>
       <c r="CM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.001044078235766537</v>
+        <v>-0.05493823451706907</v>
       </c>
       <c r="CO10" t="n">
         <v>-0</v>
       </c>
       <c r="CP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.004414831211043778</v>
+        <v>0.04289412113420577</v>
       </c>
       <c r="CR10" t="n">
-        <v>-0.007518047943929835</v>
+        <v>0.03854001740774602</v>
       </c>
       <c r="CS10" t="n">
         <v>-0</v>
       </c>
       <c r="CT10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU10" t="n">
         <v>-0</v>
       </c>
       <c r="CV10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CW10" t="n">
-        <v>-0.02039472769586598</v>
+        <v>-0.1349765829567921</v>
       </c>
       <c r="CX10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY10" t="n">
         <v>0</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.00731297993397732</v>
+        <v>0.02604317935420485</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.02868066624101028</v>
+        <v>0.1285848658824544</v>
       </c>
       <c r="DB10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC10" t="n">
         <v>-0</v>
       </c>
       <c r="DD10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE10" t="n">
         <v>-0</v>
       </c>
       <c r="DF10" t="n">
-        <v>-0.03447946934573446</v>
+        <v>-0.08096932689126471</v>
       </c>
       <c r="DG10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0383600096285184</v>
+        <v>-0.1501347986699728</v>
       </c>
       <c r="DJ10" t="n">
-        <v>-0.0003480882909733979</v>
+        <v>0.03543732105898681</v>
       </c>
       <c r="DK10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DM10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN10" t="n">
         <v>-0</v>
       </c>
       <c r="DO10" t="n">
-        <v>-0.007928235444414461</v>
+        <v>-0.02885060514350518</v>
       </c>
       <c r="DP10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR10" t="n">
-        <v>0.005385347577786728</v>
+        <v>-0.07084754530504034</v>
       </c>
       <c r="DS10" t="n">
-        <v>-0.005879935292152946</v>
+        <v>0.02061797151759243</v>
       </c>
       <c r="DT10" t="n">
         <v>-0</v>
       </c>
       <c r="DU10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX10" t="n">
-        <v>-0.02996500409784866</v>
+        <v>-0.02909016546044193</v>
       </c>
       <c r="DY10" t="n">
         <v>0</v>
@@ -5941,10 +5941,10 @@
         <v>-0</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.01884052139693086</v>
+        <v>-0.0001595147486211558</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.02155046834119102</v>
+        <v>0.09687467420603023</v>
       </c>
       <c r="EC10" t="n">
         <v>-0</v>
@@ -5953,28 +5953,28 @@
         <v>0</v>
       </c>
       <c r="EE10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG10" t="n">
-        <v>-0.02724540126222329</v>
+        <v>-0.05771603922375268</v>
       </c>
       <c r="EH10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI10" t="n">
         <v>0</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.01344778616172645</v>
+        <v>0.006744304070362359</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.03024571752233485</v>
+        <v>0.03253540753317712</v>
       </c>
       <c r="EL10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM10" t="n">
         <v>-0</v>
@@ -5983,37 +5983,37 @@
         <v>0</v>
       </c>
       <c r="EO10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP10" t="n">
-        <v>-0.01368021858918679</v>
+        <v>-0.01497512065526038</v>
       </c>
       <c r="EQ10" t="n">
         <v>-0</v>
       </c>
       <c r="ER10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.01945940696908119</v>
+        <v>-0.01190513941654449</v>
       </c>
       <c r="ET10" t="n">
-        <v>-0.001534280044703618</v>
+        <v>0.1114175422456035</v>
       </c>
       <c r="EU10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV10" t="n">
         <v>0</v>
       </c>
       <c r="EW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY10" t="n">
-        <v>-0.01968967036175339</v>
+        <v>-0.1499151378222721</v>
       </c>
       <c r="EZ10" t="n">
         <v>-0</v>
@@ -6022,43 +6022,43 @@
         <v>-0</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.01032058013238543</v>
+        <v>0.004503766294184686</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.03140297005211409</v>
+        <v>0.09191037303808236</v>
       </c>
       <c r="FD10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE10" t="n">
         <v>-0</v>
       </c>
       <c r="FF10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG10" t="n">
         <v>0</v>
       </c>
       <c r="FH10" t="n">
-        <v>-0.01679051861931863</v>
+        <v>0.2101564110355418</v>
       </c>
       <c r="FI10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ10" t="n">
         <v>-0</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0159748079566695</v>
+        <v>-0.06998426469410322</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.01496293674793574</v>
+        <v>0.1285195439350169</v>
       </c>
       <c r="FM10" t="n">
         <v>0</v>
       </c>
       <c r="FN10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO10" t="n">
         <v>0</v>
@@ -6067,46 +6067,46 @@
         <v>0</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.004508800564165339</v>
+        <v>0.050931121643411</v>
       </c>
       <c r="FR10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS10" t="n">
         <v>-0</v>
       </c>
       <c r="FT10" t="n">
-        <v>-0.0239823349732586</v>
+        <v>-0.07810080430218319</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.001727154148208447</v>
+        <v>-0.09536503972263018</v>
       </c>
       <c r="FV10" t="n">
         <v>-0</v>
       </c>
       <c r="FW10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.005322960670697717</v>
+        <v>-0.03342678394748459</v>
       </c>
       <c r="GA10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB10" t="n">
         <v>-0</v>
       </c>
       <c r="GC10" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD10" t="n">
-        <v>-0.005368888271155104</v>
+        <v>0.1300105647484201</v>
       </c>
       <c r="GE10" t="n">
         <v>-0</v>
@@ -6115,7 +6115,7 @@
         <v>-0</v>
       </c>
       <c r="GG10" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -6123,22 +6123,22 @@
         <v>0</v>
       </c>
       <c r="B11" t="n">
-        <v>0.3041267767614614</v>
+        <v>0.3231924340002356</v>
       </c>
       <c r="C11" t="n">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.07944696767260467</v>
+        <v>-0.1574474856984551</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0337671603386641</v>
+        <v>-0.0463482763137618</v>
       </c>
       <c r="F11" t="n">
         <v>0</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H11" t="n">
         <v>-0</v>
@@ -6150,22 +6150,22 @@
         <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2281530196259798</v>
+        <v>0.3511406980690668</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.0654441519635853</v>
+        <v>-0.14449582555669</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.04450167181251637</v>
+        <v>-0.1053017331868169</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q11" t="n">
         <v>0</v>
@@ -6177,25 +6177,25 @@
         <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>0.09520426892144021</v>
+        <v>0.04924007132295743</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0169547063983432</v>
+        <v>-0.03309842746641012</v>
       </c>
       <c r="W11" t="n">
-        <v>0.05978503822968013</v>
+        <v>-0.1128579684055137</v>
       </c>
       <c r="X11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
         <v>-0</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -6204,43 +6204,43 @@
         <v>-0</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.1319022583999126</v>
+        <v>-0.02802150053440534</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="n">
-        <v>-0.04610901995692983</v>
+        <v>-0.1469341927268848</v>
       </c>
       <c r="AF11" t="n">
-        <v>-0.06551759911350233</v>
+        <v>-0.08955256619830691</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AH11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK11" t="n">
         <v>0</v>
       </c>
       <c r="AL11" t="n">
-        <v>0.02616553386563628</v>
+        <v>0.1257859440853083</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>-0.06803660098714695</v>
+        <v>-0.121333864045971</v>
       </c>
       <c r="AO11" t="n">
-        <v>-0.0476210516078717</v>
+        <v>0.01602135288536183</v>
       </c>
       <c r="AP11" t="n">
         <v>0</v>
@@ -6249,7 +6249,7 @@
         <v>0</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS11" t="n">
         <v>0</v>
@@ -6258,16 +6258,16 @@
         <v>-0</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.3555154206267067</v>
+        <v>0.3512102689747046</v>
       </c>
       <c r="AV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>-0.02396879432876483</v>
+        <v>-0.2537966742790898</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.1246799456520706</v>
+        <v>-0.3447488891394216</v>
       </c>
       <c r="AY11" t="n">
         <v>-0</v>
@@ -6276,7 +6276,7 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB11" t="n">
         <v>-0</v>
@@ -6285,16 +6285,16 @@
         <v>-0</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.03255030966877175</v>
+        <v>-0.03703015587206291</v>
       </c>
       <c r="BE11" t="n">
         <v>0</v>
       </c>
       <c r="BF11" t="n">
-        <v>-0.05551148549638381</v>
+        <v>-0.02079783036646823</v>
       </c>
       <c r="BG11" t="n">
-        <v>-0.1760332552659136</v>
+        <v>0.06121724172154895</v>
       </c>
       <c r="BH11" t="n">
         <v>0</v>
@@ -6303,7 +6303,7 @@
         <v>-0</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK11" t="n">
         <v>0</v>
@@ -6312,76 +6312,76 @@
         <v>-0</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.03579652113615843</v>
+        <v>0.02971412516063013</v>
       </c>
       <c r="BN11" t="n">
         <v>-0</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.09546420936147998</v>
+        <v>0.1048685104532388</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.1088155932183493</v>
+        <v>0.01312217992016203</v>
       </c>
       <c r="BQ11" t="n">
         <v>-0</v>
       </c>
       <c r="BR11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS11" t="n">
         <v>-0</v>
       </c>
       <c r="BT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU11" t="n">
         <v>0</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.202392100328228</v>
+        <v>0.2573501456768331</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.0009175871886238721</v>
+        <v>-0.1699032474227</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.04900493908349321</v>
+        <v>-0.1198990013304092</v>
       </c>
       <c r="BZ11" t="n">
         <v>0</v>
       </c>
       <c r="CA11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CB11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD11" t="n">
         <v>-0</v>
       </c>
       <c r="CE11" t="n">
-        <v>-0.08999001611180633</v>
+        <v>-0.1430010109757761</v>
       </c>
       <c r="CF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.01727573185775867</v>
+        <v>0.1846524949780959</v>
       </c>
       <c r="CH11" t="n">
-        <v>-0.002528439247817448</v>
+        <v>0.01014995527147892</v>
       </c>
       <c r="CI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CJ11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK11" t="n">
         <v>0</v>
@@ -6393,49 +6393,49 @@
         <v>0</v>
       </c>
       <c r="CN11" t="n">
-        <v>-0.01359587497526173</v>
+        <v>-0.02935831351470632</v>
       </c>
       <c r="CO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP11" t="n">
-        <v>-0.02271059506019469</v>
+        <v>0.05965536492576685</v>
       </c>
       <c r="CQ11" t="n">
-        <v>-0.02025952320216804</v>
+        <v>0.02796366470161803</v>
       </c>
       <c r="CR11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU11" t="n">
         <v>-0</v>
       </c>
       <c r="CV11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW11" t="n">
-        <v>-0.07541447755884395</v>
+        <v>-0.1350638285101804</v>
       </c>
       <c r="CX11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.04047462635582431</v>
+        <v>0.1911969260975924</v>
       </c>
       <c r="CZ11" t="n">
-        <v>-0.002143794457877505</v>
+        <v>0.02583406340817293</v>
       </c>
       <c r="DA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC11" t="n">
         <v>-0</v>
@@ -6447,22 +6447,22 @@
         <v>0</v>
       </c>
       <c r="DF11" t="n">
-        <v>-0.01171508161622276</v>
+        <v>-0.09217969328015178</v>
       </c>
       <c r="DG11" t="n">
         <v>0</v>
       </c>
       <c r="DH11" t="n">
-        <v>-0.0005064193716877428</v>
+        <v>-0.01454797744859072</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0005158961975796625</v>
+        <v>-0.1281813144431907</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DK11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DL11" t="n">
         <v>0</v>
@@ -6471,25 +6471,25 @@
         <v>0</v>
       </c>
       <c r="DN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>-0.05732808368393926</v>
+        <v>-0.07257639520211834</v>
       </c>
       <c r="DP11" t="n">
         <v>-0</v>
       </c>
       <c r="DQ11" t="n">
-        <v>-0.0537891126798741</v>
+        <v>0.07069617948379317</v>
       </c>
       <c r="DR11" t="n">
-        <v>-0.07017128268831267</v>
+        <v>-0.008947323173724224</v>
       </c>
       <c r="DS11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU11" t="n">
         <v>-0</v>
@@ -6498,106 +6498,106 @@
         <v>0</v>
       </c>
       <c r="DW11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX11" t="n">
-        <v>-0.01253964608854623</v>
+        <v>0.005942283753524317</v>
       </c>
       <c r="DY11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ11" t="n">
-        <v>-0.02166087378417396</v>
+        <v>0.08226374559247093</v>
       </c>
       <c r="EA11" t="n">
-        <v>-0.01426526995046999</v>
+        <v>-0.02167735170364419</v>
       </c>
       <c r="EB11" t="n">
         <v>0</v>
       </c>
       <c r="EC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EG11" t="n">
-        <v>-0.05557419230016485</v>
+        <v>-0.08687490173899323</v>
       </c>
       <c r="EH11" t="n">
         <v>0</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.02889320963818383</v>
+        <v>0.1306301411940085</v>
       </c>
       <c r="EJ11" t="n">
-        <v>0.09170814535274439</v>
+        <v>0.03465822094495143</v>
       </c>
       <c r="EK11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EL11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP11" t="n">
-        <v>-0.07823818281081436</v>
+        <v>-0.06898503872046434</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER11" t="n">
-        <v>-0.08543434209851064</v>
+        <v>-0.1164081652566985</v>
       </c>
       <c r="ES11" t="n">
-        <v>-0.01285914379528745</v>
+        <v>-0.03542310064310383</v>
       </c>
       <c r="ET11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV11" t="n">
         <v>0</v>
       </c>
       <c r="EW11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX11" t="n">
         <v>-0</v>
       </c>
       <c r="EY11" t="n">
-        <v>-0.07920099059611359</v>
+        <v>-0.1551642205343335</v>
       </c>
       <c r="EZ11" t="n">
         <v>-0</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.02680567836240331</v>
+        <v>0.2138370339984647</v>
       </c>
       <c r="FB11" t="n">
-        <v>-0.006436687019389604</v>
+        <v>-0.003491838856021417</v>
       </c>
       <c r="FC11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE11" t="n">
         <v>0</v>
@@ -6609,49 +6609,49 @@
         <v>0</v>
       </c>
       <c r="FH11" t="n">
-        <v>-0.00744759997392381</v>
+        <v>0.1481265500203002</v>
       </c>
       <c r="FI11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.04965294011384581</v>
+        <v>0.1652531964776545</v>
       </c>
       <c r="FK11" t="n">
-        <v>-0.03095888140158225</v>
+        <v>0.008241731363338204</v>
       </c>
       <c r="FL11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FM11" t="n">
         <v>0</v>
       </c>
       <c r="FN11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.002443531002751255</v>
+        <v>0.04994094956009525</v>
       </c>
       <c r="FR11" t="n">
         <v>-0</v>
       </c>
       <c r="FS11" t="n">
-        <v>0.07387986065508181</v>
+        <v>0.2355011723908654</v>
       </c>
       <c r="FT11" t="n">
-        <v>0.02707628372713808</v>
+        <v>-0.05190050385717333</v>
       </c>
       <c r="FU11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FW11" t="n">
         <v>0</v>
@@ -6660,39 +6660,39 @@
         <v>0</v>
       </c>
       <c r="FY11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ11" t="n">
-        <v>-0.02408872291696919</v>
+        <v>-0.05504192022865539</v>
       </c>
       <c r="GA11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB11" t="n">
-        <v>-0.02974876786586001</v>
+        <v>0.1437758895577512</v>
       </c>
       <c r="GC11" t="n">
         <v>0</v>
       </c>
       <c r="GD11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE11" t="n">
         <v>-0</v>
       </c>
       <c r="GF11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG11" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B12" t="n">
-        <v>0.1774618845533465</v>
+        <v>0.3267278418791099</v>
       </c>
       <c r="C12" t="n">
         <v>0</v>
@@ -6701,10 +6701,10 @@
         <v>0</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.04804408566546823</v>
+        <v>0.02406191874875207</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.1175756295394787</v>
+        <v>-0.2994092411231976</v>
       </c>
       <c r="G12" t="n">
         <v>-0</v>
@@ -6713,13 +6713,13 @@
         <v>-0</v>
       </c>
       <c r="I12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K12" t="n">
-        <v>0.1521067439743989</v>
+        <v>0.4095087179897669</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -6728,25 +6728,25 @@
         <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.01627300610532379</v>
+        <v>-0.1249078739959048</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.07696903691843332</v>
+        <v>-0.2866756528864594</v>
       </c>
       <c r="P12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T12" t="n">
-        <v>0.03182302377754161</v>
+        <v>0.1200614154582821</v>
       </c>
       <c r="U12" t="n">
         <v>-0</v>
@@ -6755,37 +6755,37 @@
         <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.02862698168781971</v>
+        <v>-0.07804943586715693</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.0003495146993050758</v>
+        <v>-0.09125517577351512</v>
       </c>
       <c r="Y12" t="n">
         <v>-0</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB12" t="n">
         <v>-0</v>
       </c>
       <c r="AC12" t="n">
-        <v>-0.00228482560609198</v>
+        <v>-0.07070651874472823</v>
       </c>
       <c r="AD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>-0.0008747245431520338</v>
+        <v>-0.2317141333113936</v>
       </c>
       <c r="AG12" t="n">
-        <v>-0.008968006854129093</v>
+        <v>0.07110474651469686</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -6794,28 +6794,28 @@
         <v>-0</v>
       </c>
       <c r="AJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK12" t="n">
         <v>0</v>
       </c>
       <c r="AL12" t="n">
-        <v>0.02640756563704421</v>
+        <v>0.1311233889063309</v>
       </c>
       <c r="AM12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO12" t="n">
-        <v>-0.009683204145728116</v>
+        <v>-0.03667330238049162</v>
       </c>
       <c r="AP12" t="n">
-        <v>-0.05310058128740785</v>
+        <v>-0.08925492589453622</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR12" t="n">
         <v>-0</v>
@@ -6824,37 +6824,37 @@
         <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU12" t="n">
-        <v>0.1528534643943812</v>
+        <v>0.6005830446290951</v>
       </c>
       <c r="AV12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW12" t="n">
         <v>0</v>
       </c>
       <c r="AX12" t="n">
-        <v>-0.03734727186145556</v>
+        <v>-0.2840621283746746</v>
       </c>
       <c r="AY12" t="n">
-        <v>-0.1161542728417131</v>
+        <v>-0.3341586469428531</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD12" t="n">
-        <v>0.05233599532775377</v>
+        <v>-0.1302135184988792</v>
       </c>
       <c r="BE12" t="n">
         <v>0</v>
@@ -6863,25 +6863,25 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>-0.04833762042083375</v>
+        <v>0.02537528550495153</v>
       </c>
       <c r="BH12" t="n">
-        <v>-0.0491269410728273</v>
+        <v>-0.04948546557955492</v>
       </c>
       <c r="BI12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BJ12" t="n">
         <v>-0</v>
       </c>
       <c r="BK12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.04964417299871704</v>
+        <v>0.122603175158843</v>
       </c>
       <c r="BN12" t="n">
         <v>-0</v>
@@ -6890,79 +6890,79 @@
         <v>-0</v>
       </c>
       <c r="BP12" t="n">
-        <v>0.02317401838687887</v>
+        <v>0.06006134488654192</v>
       </c>
       <c r="BQ12" t="n">
-        <v>0.004534260766278887</v>
+        <v>0.07595451907731803</v>
       </c>
       <c r="BR12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU12" t="n">
         <v>-0</v>
       </c>
       <c r="BV12" t="n">
-        <v>0.08830141853826382</v>
+        <v>0.3282128859413526</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX12" t="n">
         <v>0</v>
       </c>
       <c r="BY12" t="n">
-        <v>-0.02551131689542412</v>
+        <v>-0.08303979108529336</v>
       </c>
       <c r="BZ12" t="n">
-        <v>-0.03422336445025529</v>
+        <v>-0.1900692109545795</v>
       </c>
       <c r="CA12" t="n">
         <v>-0</v>
       </c>
       <c r="CB12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC12" t="n">
         <v>-0</v>
       </c>
       <c r="CD12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE12" t="n">
-        <v>-0.0426960855627903</v>
+        <v>-0.1604278534875037</v>
       </c>
       <c r="CF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG12" t="n">
         <v>-0</v>
       </c>
       <c r="CH12" t="n">
-        <v>0.002064841516864209</v>
+        <v>0.04702512115010715</v>
       </c>
       <c r="CI12" t="n">
-        <v>0.03709441325662847</v>
+        <v>0.1081047025755514</v>
       </c>
       <c r="CJ12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK12" t="n">
         <v>0</v>
       </c>
       <c r="CL12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CM12" t="n">
         <v>0</v>
       </c>
       <c r="CN12" t="n">
-        <v>0.0002524096796776107</v>
+        <v>-0.08753840176149605</v>
       </c>
       <c r="CO12" t="n">
         <v>-0</v>
@@ -6971,37 +6971,37 @@
         <v>-0</v>
       </c>
       <c r="CQ12" t="n">
-        <v>0.001137313638678613</v>
+        <v>0.09963615112846497</v>
       </c>
       <c r="CR12" t="n">
-        <v>-0.01292647560800126</v>
+        <v>-0.007977278208731564</v>
       </c>
       <c r="CS12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV12" t="n">
         <v>-0</v>
       </c>
       <c r="CW12" t="n">
-        <v>-0.03780652974364755</v>
+        <v>-0.1515039884947151</v>
       </c>
       <c r="CX12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY12" t="n">
         <v>0</v>
       </c>
       <c r="CZ12" t="n">
-        <v>0.006945445538257791</v>
+        <v>0.02850391881786214</v>
       </c>
       <c r="DA12" t="n">
-        <v>0.04040790321084167</v>
+        <v>0.1413611711041263</v>
       </c>
       <c r="DB12" t="n">
         <v>0</v>
@@ -7010,25 +7010,25 @@
         <v>-0</v>
       </c>
       <c r="DD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE12" t="n">
         <v>0</v>
       </c>
       <c r="DF12" t="n">
-        <v>0.00611381714759533</v>
+        <v>0.02385372150422842</v>
       </c>
       <c r="DG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DH12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05425811866621269</v>
+        <v>-0.02759887334081863</v>
       </c>
       <c r="DJ12" t="n">
-        <v>0.001849885853411415</v>
+        <v>0.03909356381199871</v>
       </c>
       <c r="DK12" t="n">
         <v>0</v>
@@ -7037,13 +7037,13 @@
         <v>0</v>
       </c>
       <c r="DM12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN12" t="n">
         <v>-0</v>
       </c>
       <c r="DO12" t="n">
-        <v>-0.02003496397438697</v>
+        <v>-0.135302937176847</v>
       </c>
       <c r="DP12" t="n">
         <v>0</v>
@@ -7052,25 +7052,25 @@
         <v>0</v>
       </c>
       <c r="DR12" t="n">
-        <v>0.01486257327730923</v>
+        <v>0.02808381033978298</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.009253161033919382</v>
+        <v>0.1787556096428484</v>
       </c>
       <c r="DT12" t="n">
         <v>-0</v>
       </c>
       <c r="DU12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV12" t="n">
         <v>0</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DX12" t="n">
-        <v>-0.04823800017351424</v>
+        <v>-0.1007681039403984</v>
       </c>
       <c r="DY12" t="n">
         <v>-0</v>
@@ -7079,37 +7079,37 @@
         <v>-0</v>
       </c>
       <c r="EA12" t="n">
-        <v>0.03128580391230212</v>
+        <v>0.1072658518521084</v>
       </c>
       <c r="EB12" t="n">
-        <v>0.01650633670439284</v>
+        <v>0.05381994443565959</v>
       </c>
       <c r="EC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED12" t="n">
         <v>0</v>
       </c>
       <c r="EE12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF12" t="n">
         <v>0</v>
       </c>
       <c r="EG12" t="n">
-        <v>-0.03632211996327393</v>
+        <v>-0.0283609205348149</v>
       </c>
       <c r="EH12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI12" t="n">
         <v>-0</v>
       </c>
       <c r="EJ12" t="n">
-        <v>0.01284293478245575</v>
+        <v>-0.03643655403467658</v>
       </c>
       <c r="EK12" t="n">
-        <v>0.03734275217215383</v>
+        <v>0.01052564012963434</v>
       </c>
       <c r="EL12" t="n">
         <v>-0</v>
@@ -7118,13 +7118,13 @@
         <v>-0</v>
       </c>
       <c r="EN12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO12" t="n">
         <v>0</v>
       </c>
       <c r="EP12" t="n">
-        <v>-0.03403833236071764</v>
+        <v>-0.04228860564171729</v>
       </c>
       <c r="EQ12" t="n">
         <v>-0</v>
@@ -7133,13 +7133,13 @@
         <v>-0</v>
       </c>
       <c r="ES12" t="n">
-        <v>-0.005873485944490737</v>
+        <v>-0.1131297656285994</v>
       </c>
       <c r="ET12" t="n">
-        <v>0.006608376008677746</v>
+        <v>0.02491066170184096</v>
       </c>
       <c r="EU12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV12" t="n">
         <v>0</v>
@@ -7151,7 +7151,7 @@
         <v>0</v>
       </c>
       <c r="EY12" t="n">
-        <v>-0.03780404859297667</v>
+        <v>-0.1747840917684477</v>
       </c>
       <c r="EZ12" t="n">
         <v>-0</v>
@@ -7160,25 +7160,25 @@
         <v>-0</v>
       </c>
       <c r="FB12" t="n">
-        <v>0.008499741856094388</v>
+        <v>0.02042971761116</v>
       </c>
       <c r="FC12" t="n">
-        <v>0.03833762558058384</v>
+        <v>0.1297150203163657</v>
       </c>
       <c r="FD12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE12" t="n">
         <v>0</v>
       </c>
       <c r="FF12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG12" t="n">
         <v>0</v>
       </c>
       <c r="FH12" t="n">
-        <v>-0.02331342039897978</v>
+        <v>0.09936886280870076</v>
       </c>
       <c r="FI12" t="n">
         <v>0</v>
@@ -7187,25 +7187,25 @@
         <v>-0</v>
       </c>
       <c r="FK12" t="n">
-        <v>0.01144635592023375</v>
+        <v>-0.03999822995791748</v>
       </c>
       <c r="FL12" t="n">
-        <v>0.03574985519741991</v>
+        <v>0.1478808204125222</v>
       </c>
       <c r="FM12" t="n">
         <v>0</v>
       </c>
       <c r="FN12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO12" t="n">
         <v>0</v>
       </c>
       <c r="FP12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ12" t="n">
-        <v>-0.002933223403480311</v>
+        <v>0.02798053055444245</v>
       </c>
       <c r="FR12" t="n">
         <v>-0</v>
@@ -7214,37 +7214,37 @@
         <v>-0</v>
       </c>
       <c r="FT12" t="n">
-        <v>-0.02663353189099168</v>
+        <v>-0.07360766302314259</v>
       </c>
       <c r="FU12" t="n">
-        <v>0.021875456413417</v>
+        <v>-0.02349412265553791</v>
       </c>
       <c r="FV12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ12" t="n">
-        <v>-0.003310714661828454</v>
+        <v>-0.03917366038157794</v>
       </c>
       <c r="GA12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB12" t="n">
         <v>-0</v>
       </c>
       <c r="GC12" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD12" t="n">
-        <v>-0.01871974115312633</v>
+        <v>0.1530369439561523</v>
       </c>
       <c r="GE12" t="n">
         <v>-0</v>
@@ -7253,7 +7253,7 @@
         <v>-0</v>
       </c>
       <c r="GG12" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -7261,46 +7261,46 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0.2966100372177339</v>
+        <v>0.2650235815935421</v>
       </c>
       <c r="C13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.09251972744736088</v>
+        <v>-0.1379324905865146</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.06748450314023292</v>
+        <v>0.0004349970177664199</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.03727931121430023</v>
+        <v>-0.0986521905440574</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2462414960894206</v>
+        <v>0.3572314264604474</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.06323117368119831</v>
+        <v>-0.1642965293081073</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.04989109041129199</v>
+        <v>-0.07528796732193727</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.03758790430219033</v>
+        <v>-0.086287594564301</v>
       </c>
       <c r="P13" t="n">
         <v>-0</v>
@@ -7315,133 +7315,133 @@
         <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>0.07824064031665799</v>
+        <v>0.1069363088159009</v>
       </c>
       <c r="U13" t="n">
         <v>-0</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.02495468807201317</v>
+        <v>-0.091270943377357</v>
       </c>
       <c r="W13" t="n">
-        <v>0.041574818616316</v>
+        <v>-0.1216784981544768</v>
       </c>
       <c r="X13" t="n">
-        <v>0.01134099364354196</v>
+        <v>-0.0868788456875534</v>
       </c>
       <c r="Y13" t="n">
         <v>-0</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0.05498497229725322</v>
+        <v>-0.1005251922778254</v>
       </c>
       <c r="AD13" t="n">
         <v>-0</v>
       </c>
       <c r="AE13" t="n">
-        <v>0.01204503911599231</v>
+        <v>-0.116016493005078</v>
       </c>
       <c r="AF13" t="n">
-        <v>-0.01354466039631152</v>
+        <v>-0.09928937726451728</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.01708847235848042</v>
+        <v>0.07013341621967789</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>0</v>
       </c>
       <c r="AL13" t="n">
-        <v>0.01905949238737632</v>
+        <v>0.08355906004428459</v>
       </c>
       <c r="AM13" t="n">
         <v>-0</v>
       </c>
       <c r="AN13" t="n">
-        <v>-0.05663539425623951</v>
+        <v>-0.0813820618535807</v>
       </c>
       <c r="AO13" t="n">
-        <v>-0.05403336755295805</v>
+        <v>0.0026366175817969</v>
       </c>
       <c r="AP13" t="n">
-        <v>-0.04219881775711441</v>
+        <v>-0.03875106505860565</v>
       </c>
       <c r="AQ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
       <c r="AU13" t="n">
-        <v>0.2885058195484158</v>
+        <v>0.4124387240801216</v>
       </c>
       <c r="AV13" t="n">
         <v>-0</v>
       </c>
       <c r="AW13" t="n">
-        <v>-0.03749721060397475</v>
+        <v>-0.1546768629638886</v>
       </c>
       <c r="AX13" t="n">
-        <v>0.03235513206781332</v>
+        <v>-0.2218920322796608</v>
       </c>
       <c r="AY13" t="n">
-        <v>0.02482680063354763</v>
+        <v>-0.1552104450500904</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB13" t="n">
         <v>-0</v>
       </c>
       <c r="BC13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD13" t="n">
-        <v>0.04818761496071487</v>
+        <v>-0.07897686238581599</v>
       </c>
       <c r="BE13" t="n">
         <v>0</v>
       </c>
       <c r="BF13" t="n">
-        <v>-0.06299947960859739</v>
+        <v>-0.08627166866974063</v>
       </c>
       <c r="BG13" t="n">
-        <v>-0.1092746393109315</v>
+        <v>0.009196117891978885</v>
       </c>
       <c r="BH13" t="n">
-        <v>-0.04926506270783808</v>
+        <v>-0.07655322976420117</v>
       </c>
       <c r="BI13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK13" t="n">
         <v>0</v>
@@ -7450,19 +7450,19 @@
         <v>-0</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.0675591551168373</v>
+        <v>0.03832113188737277</v>
       </c>
       <c r="BN13" t="n">
         <v>-0</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.05108264766477009</v>
+        <v>0.1192452836990254</v>
       </c>
       <c r="BP13" t="n">
-        <v>0.09918260135572098</v>
+        <v>-0.007089782682484685</v>
       </c>
       <c r="BQ13" t="n">
-        <v>0.03697479759525464</v>
+        <v>-0.004149789110640175</v>
       </c>
       <c r="BR13" t="n">
         <v>0</v>
@@ -7471,31 +7471,31 @@
         <v>-0</v>
       </c>
       <c r="BT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU13" t="n">
         <v>0</v>
       </c>
       <c r="BV13" t="n">
-        <v>0.1345310958844833</v>
+        <v>0.247458160477787</v>
       </c>
       <c r="BW13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX13" t="n">
-        <v>0.00201939559197415</v>
+        <v>-0.1208391319740486</v>
       </c>
       <c r="BY13" t="n">
-        <v>0.02245707613755304</v>
+        <v>-0.06269209755008548</v>
       </c>
       <c r="BZ13" t="n">
-        <v>0.01372309285657461</v>
+        <v>-0.1295617732772306</v>
       </c>
       <c r="CA13" t="n">
         <v>-0</v>
       </c>
       <c r="CB13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC13" t="n">
         <v>-0</v>
@@ -7504,22 +7504,22 @@
         <v>0</v>
       </c>
       <c r="CE13" t="n">
-        <v>-0.07142502792888485</v>
+        <v>-0.09389816087809043</v>
       </c>
       <c r="CF13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG13" t="n">
-        <v>0.0104552731082974</v>
+        <v>0.1040599153501385</v>
       </c>
       <c r="CH13" t="n">
-        <v>-0.002659918355594485</v>
+        <v>0.0101282232832265</v>
       </c>
       <c r="CI13" t="n">
-        <v>0.02396518348049048</v>
+        <v>0.03189014068335585</v>
       </c>
       <c r="CJ13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK13" t="n">
         <v>0</v>
@@ -7531,46 +7531,46 @@
         <v>0</v>
       </c>
       <c r="CN13" t="n">
-        <v>-0.003063618586850321</v>
+        <v>-0.03398708635356668</v>
       </c>
       <c r="CO13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP13" t="n">
-        <v>-0.02718205369307522</v>
+        <v>0.1081822439394901</v>
       </c>
       <c r="CQ13" t="n">
-        <v>-0.03244922505246275</v>
+        <v>0.06326796765863295</v>
       </c>
       <c r="CR13" t="n">
-        <v>-0.01659622414320707</v>
+        <v>0.02477747688141905</v>
       </c>
       <c r="CS13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW13" t="n">
-        <v>-0.05861319959364533</v>
+        <v>-0.1021297703907073</v>
       </c>
       <c r="CX13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY13" t="n">
-        <v>0.03199759872846165</v>
+        <v>0.1311437856435474</v>
       </c>
       <c r="CZ13" t="n">
-        <v>0.001307611386036127</v>
+        <v>0.007471989605565393</v>
       </c>
       <c r="DA13" t="n">
-        <v>0.02543322536536964</v>
+        <v>0.05734106451857649</v>
       </c>
       <c r="DB13" t="n">
         <v>0</v>
@@ -7585,19 +7585,19 @@
         <v>0</v>
       </c>
       <c r="DF13" t="n">
-        <v>-0.03189863012438825</v>
+        <v>-0.04468476347183269</v>
       </c>
       <c r="DG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH13" t="n">
-        <v>0.04326940263664507</v>
+        <v>0.03112955003656362</v>
       </c>
       <c r="DI13" t="n">
-        <v>-0.004164121119110139</v>
+        <v>0.008658707252920115</v>
       </c>
       <c r="DJ13" t="n">
-        <v>0.01123783123593995</v>
+        <v>0.02136016027009907</v>
       </c>
       <c r="DK13" t="n">
         <v>-0</v>
@@ -7606,31 +7606,31 @@
         <v>0</v>
       </c>
       <c r="DM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO13" t="n">
-        <v>-0.01978872254523345</v>
+        <v>-0.009863185598840484</v>
       </c>
       <c r="DP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ13" t="n">
-        <v>0.03752325915282668</v>
+        <v>0.03268664825647465</v>
       </c>
       <c r="DR13" t="n">
-        <v>-0.01744772156067373</v>
+        <v>-0.07932596235267823</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.0192804475848472</v>
+        <v>-0.01216308865538179</v>
       </c>
       <c r="DT13" t="n">
         <v>-0</v>
       </c>
       <c r="DU13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV13" t="n">
         <v>0</v>
@@ -7639,76 +7639,76 @@
         <v>-0</v>
       </c>
       <c r="DX13" t="n">
-        <v>-0.03701863200230176</v>
+        <v>-0.02073822932834549</v>
       </c>
       <c r="DY13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ13" t="n">
-        <v>-0.01582650519299933</v>
+        <v>0.08015446326707294</v>
       </c>
       <c r="EA13" t="n">
-        <v>0.02080704078435784</v>
+        <v>0.009718159876766589</v>
       </c>
       <c r="EB13" t="n">
-        <v>0.03469767167618117</v>
+        <v>-0.02407523121696089</v>
       </c>
       <c r="EC13" t="n">
         <v>0</v>
       </c>
       <c r="ED13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF13" t="n">
         <v>0</v>
       </c>
       <c r="EG13" t="n">
-        <v>-0.0762907810176289</v>
+        <v>-0.04982838985179795</v>
       </c>
       <c r="EH13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI13" t="n">
-        <v>0.03275148298971785</v>
+        <v>0.09146056534737228</v>
       </c>
       <c r="EJ13" t="n">
-        <v>0.05245926360818354</v>
+        <v>0.02292942428992237</v>
       </c>
       <c r="EK13" t="n">
-        <v>0.01751778003416754</v>
+        <v>-0.04528716709403947</v>
       </c>
       <c r="EL13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM13" t="n">
         <v>-0</v>
       </c>
       <c r="EN13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO13" t="n">
         <v>0</v>
       </c>
       <c r="EP13" t="n">
-        <v>-0.05635133774628693</v>
+        <v>-0.04053373728621922</v>
       </c>
       <c r="EQ13" t="n">
         <v>-0</v>
       </c>
       <c r="ER13" t="n">
-        <v>0.02473642064280961</v>
+        <v>0.1015589165809334</v>
       </c>
       <c r="ES13" t="n">
-        <v>0.01348342162660755</v>
+        <v>-0.01373765349412954</v>
       </c>
       <c r="ET13" t="n">
-        <v>0.03290528997694995</v>
+        <v>0.0565151092256442</v>
       </c>
       <c r="EU13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV13" t="n">
         <v>0</v>
@@ -7720,22 +7720,22 @@
         <v>0</v>
       </c>
       <c r="EY13" t="n">
-        <v>-0.05899816198360345</v>
+        <v>-0.1040000081025627</v>
       </c>
       <c r="EZ13" t="n">
         <v>-0</v>
       </c>
       <c r="FA13" t="n">
-        <v>0.01352119096938438</v>
+        <v>0.147197193774934</v>
       </c>
       <c r="FB13" t="n">
-        <v>0.004753226497370896</v>
+        <v>-0.006511477387165269</v>
       </c>
       <c r="FC13" t="n">
-        <v>0.03145827143646546</v>
+        <v>0.04406568618917246</v>
       </c>
       <c r="FD13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE13" t="n">
         <v>0</v>
@@ -7744,52 +7744,52 @@
         <v>0</v>
       </c>
       <c r="FG13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FH13" t="n">
-        <v>-0.03097377320343571</v>
+        <v>0.1184556621397233</v>
       </c>
       <c r="FI13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ13" t="n">
-        <v>0.0362130091591101</v>
+        <v>0.118410885851253</v>
       </c>
       <c r="FK13" t="n">
-        <v>0.009190056019668423</v>
+        <v>-0.02287918713009233</v>
       </c>
       <c r="FL13" t="n">
-        <v>-0.01099178370024969</v>
+        <v>0.1281788053253084</v>
       </c>
       <c r="FM13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FN13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO13" t="n">
         <v>0</v>
       </c>
       <c r="FP13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ13" t="n">
-        <v>-0.004925342165696881</v>
+        <v>0.01477864957724929</v>
       </c>
       <c r="FR13" t="n">
         <v>0</v>
       </c>
       <c r="FS13" t="n">
-        <v>0.009754397028229767</v>
+        <v>0.1449261815928986</v>
       </c>
       <c r="FT13" t="n">
-        <v>-0.0319724870451904</v>
+        <v>-0.04733007337410144</v>
       </c>
       <c r="FU13" t="n">
-        <v>0.01902404609222003</v>
+        <v>-0.02024695528159818</v>
       </c>
       <c r="FV13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FW13" t="n">
         <v>0</v>
@@ -7798,25 +7798,25 @@
         <v>0</v>
       </c>
       <c r="FY13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ13" t="n">
-        <v>0.01709206540651812</v>
+        <v>-0.01811262352142722</v>
       </c>
       <c r="GA13" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB13" t="n">
-        <v>-0.05282979881343404</v>
+        <v>0.03145786624234143</v>
       </c>
       <c r="GC13" t="n">
         <v>-0</v>
       </c>
       <c r="GD13" t="n">
-        <v>-0.03038564527008909</v>
+        <v>0.1089046105800843</v>
       </c>
       <c r="GE13" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF13" t="n">
         <v>0</v>
@@ -7830,46 +7830,46 @@
         <v>0</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2375549490567123</v>
+        <v>0.1636963602384493</v>
       </c>
       <c r="C14" t="n">
         <v>0</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.07163675892320907</v>
+        <v>-0.09442201750671539</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.01925165910869601</v>
+        <v>-0.005563540478323244</v>
       </c>
       <c r="F14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1863934418944772</v>
+        <v>0.1998069219682524</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.07482456409222045</v>
+        <v>-0.1186311800472918</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.02972661046220002</v>
+        <v>-0.03678810146079305</v>
       </c>
       <c r="O14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
         <v>-0</v>
@@ -7884,19 +7884,19 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>0.06743187703244223</v>
+        <v>0.06150579585842699</v>
       </c>
       <c r="U14" t="n">
         <v>-0</v>
       </c>
       <c r="V14" t="n">
-        <v>0.01319258291935494</v>
+        <v>-0.04578432097692119</v>
       </c>
       <c r="W14" t="n">
-        <v>0.0738339722057602</v>
+        <v>-0.04195412530171205</v>
       </c>
       <c r="X14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>-0</v>
@@ -7905,76 +7905,76 @@
         <v>-0</v>
       </c>
       <c r="AA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC14" t="n">
-        <v>0.05845901465798675</v>
+        <v>-0.006074818309184563</v>
       </c>
       <c r="AD14" t="n">
         <v>-0</v>
       </c>
       <c r="AE14" t="n">
-        <v>-0.01969840305982016</v>
+        <v>-0.09647457126188039</v>
       </c>
       <c r="AF14" t="n">
-        <v>-0.01722052389682318</v>
+        <v>-0.03271300127037642</v>
       </c>
       <c r="AG14" t="n">
         <v>-0</v>
       </c>
       <c r="AH14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AJ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK14" t="n">
         <v>0</v>
       </c>
       <c r="AL14" t="n">
-        <v>-0.01731976884951594</v>
+        <v>0.07355966968191101</v>
       </c>
       <c r="AM14" t="n">
         <v>-0</v>
       </c>
       <c r="AN14" t="n">
-        <v>-0.05694668517625593</v>
+        <v>-0.06764489395293863</v>
       </c>
       <c r="AO14" t="n">
-        <v>-0.04653137091004816</v>
+        <v>0.03093935468959871</v>
       </c>
       <c r="AP14" t="n">
         <v>0</v>
       </c>
       <c r="AQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AS14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AT14" t="n">
         <v>0</v>
       </c>
       <c r="AU14" t="n">
-        <v>0.2243260286965259</v>
+        <v>0.1922824697208796</v>
       </c>
       <c r="AV14" t="n">
         <v>-0</v>
       </c>
       <c r="AW14" t="n">
-        <v>0.02318118332061579</v>
+        <v>-0.07540790618295933</v>
       </c>
       <c r="AX14" t="n">
-        <v>0.1025279677833229</v>
+        <v>-0.1365999449639604</v>
       </c>
       <c r="AY14" t="n">
         <v>-0</v>
@@ -7983,34 +7983,34 @@
         <v>-0</v>
       </c>
       <c r="BA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB14" t="n">
         <v>-0</v>
       </c>
       <c r="BC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BD14" t="n">
-        <v>0.02993841906775955</v>
+        <v>-0.01648984838296468</v>
       </c>
       <c r="BE14" t="n">
         <v>0</v>
       </c>
       <c r="BF14" t="n">
-        <v>-0.09923443314862934</v>
+        <v>-0.03323647788628697</v>
       </c>
       <c r="BG14" t="n">
-        <v>-0.06293298310761275</v>
+        <v>-0.0346796034212501</v>
       </c>
       <c r="BH14" t="n">
         <v>0</v>
       </c>
       <c r="BI14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK14" t="n">
         <v>0</v>
@@ -8019,19 +8019,19 @@
         <v>-0</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.0496643369697654</v>
+        <v>0.02979396299776483</v>
       </c>
       <c r="BN14" t="n">
         <v>-0</v>
       </c>
       <c r="BO14" t="n">
-        <v>0.03138441799034126</v>
+        <v>0.01999691625570401</v>
       </c>
       <c r="BP14" t="n">
-        <v>0.1490614150393862</v>
+        <v>0.03995858495553389</v>
       </c>
       <c r="BQ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BR14" t="n">
         <v>0</v>
@@ -8040,49 +8040,49 @@
         <v>-0</v>
       </c>
       <c r="BT14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU14" t="n">
         <v>0</v>
       </c>
       <c r="BV14" t="n">
-        <v>0.09679724515103988</v>
+        <v>0.1280317194141427</v>
       </c>
       <c r="BW14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX14" t="n">
-        <v>0.03040308348578757</v>
+        <v>-0.05718090296955282</v>
       </c>
       <c r="BY14" t="n">
-        <v>0.07347792370648491</v>
+        <v>-0.04155342954210864</v>
       </c>
       <c r="BZ14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CA14" t="n">
         <v>-0</v>
       </c>
       <c r="CB14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CC14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE14" t="n">
-        <v>-0.05949784281672935</v>
+        <v>-0.05542161080564443</v>
       </c>
       <c r="CF14" t="n">
         <v>-0</v>
       </c>
       <c r="CG14" t="n">
-        <v>-0.0003030521941976983</v>
+        <v>0.07067525687560641</v>
       </c>
       <c r="CH14" t="n">
-        <v>-0.008272652267834048</v>
+        <v>0.0003494111815714656</v>
       </c>
       <c r="CI14" t="n">
         <v>0</v>
@@ -8094,25 +8094,25 @@
         <v>0</v>
       </c>
       <c r="CL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CM14" t="n">
         <v>0</v>
       </c>
       <c r="CN14" t="n">
-        <v>-0.00647385925864961</v>
+        <v>-0.02950128393918903</v>
       </c>
       <c r="CO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CP14" t="n">
-        <v>-0.03811525444324815</v>
+        <v>0.1138980423472525</v>
       </c>
       <c r="CQ14" t="n">
-        <v>-0.05392370130594729</v>
+        <v>0.0336941335984301</v>
       </c>
       <c r="CR14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CS14" t="n">
         <v>-0</v>
@@ -8127,43 +8127,43 @@
         <v>0</v>
       </c>
       <c r="CW14" t="n">
-        <v>-0.046162031981967</v>
+        <v>-0.0502004542002408</v>
       </c>
       <c r="CX14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY14" t="n">
-        <v>0.0143452144869735</v>
+        <v>0.08075068124603889</v>
       </c>
       <c r="CZ14" t="n">
-        <v>-0.004858823721089496</v>
+        <v>0.004153827098783501</v>
       </c>
       <c r="DA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DB14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC14" t="n">
         <v>-0</v>
       </c>
       <c r="DD14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DE14" t="n">
         <v>0</v>
       </c>
       <c r="DF14" t="n">
-        <v>-0.03118906382127288</v>
+        <v>-0.03261457983441085</v>
       </c>
       <c r="DG14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH14" t="n">
-        <v>0.01792964553151672</v>
+        <v>0.03911591388630645</v>
       </c>
       <c r="DI14" t="n">
-        <v>0.01313078210774799</v>
+        <v>-0.05078429665130634</v>
       </c>
       <c r="DJ14" t="n">
         <v>-0</v>
@@ -8178,28 +8178,28 @@
         <v>0</v>
       </c>
       <c r="DN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO14" t="n">
-        <v>-0.02786180268549819</v>
+        <v>-0.04263882199318132</v>
       </c>
       <c r="DP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ14" t="n">
-        <v>0.05635164862323917</v>
+        <v>-0.04513951027016454</v>
       </c>
       <c r="DR14" t="n">
-        <v>-0.01748202857764404</v>
+        <v>-0.02312542686541474</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DT14" t="n">
         <v>-0</v>
       </c>
       <c r="DU14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV14" t="n">
         <v>0</v>
@@ -8208,73 +8208,73 @@
         <v>-0</v>
       </c>
       <c r="DX14" t="n">
-        <v>-0.03959586839725406</v>
+        <v>-0.009416342043884984</v>
       </c>
       <c r="DY14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ14" t="n">
-        <v>-0.002363252370538335</v>
+        <v>0.04948252811761838</v>
       </c>
       <c r="EA14" t="n">
-        <v>0.01487609660832076</v>
+        <v>-0.05796491823241793</v>
       </c>
       <c r="EB14" t="n">
         <v>0</v>
       </c>
       <c r="EC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG14" t="n">
-        <v>-0.06099423501286922</v>
+        <v>-0.02657892064409464</v>
       </c>
       <c r="EH14" t="n">
         <v>-0</v>
       </c>
       <c r="EI14" t="n">
-        <v>0.02404440214188631</v>
+        <v>0.0520195722839988</v>
       </c>
       <c r="EJ14" t="n">
-        <v>0.04984714770632032</v>
+        <v>0.02960457015029163</v>
       </c>
       <c r="EK14" t="n">
         <v>0</v>
       </c>
       <c r="EL14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP14" t="n">
-        <v>-0.04442506737572906</v>
+        <v>0.02120651450941127</v>
       </c>
       <c r="EQ14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER14" t="n">
-        <v>0.01197678256792502</v>
+        <v>0.02009309025968634</v>
       </c>
       <c r="ES14" t="n">
-        <v>0.03209548342385718</v>
+        <v>-0.02518831535020219</v>
       </c>
       <c r="ET14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EU14" t="n">
         <v>0</v>
@@ -8283,49 +8283,49 @@
         <v>0</v>
       </c>
       <c r="EW14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY14" t="n">
-        <v>-0.0471441917167273</v>
+        <v>-0.06049851991208113</v>
       </c>
       <c r="EZ14" t="n">
         <v>-0</v>
       </c>
       <c r="FA14" t="n">
-        <v>-0.004511494091944238</v>
+        <v>0.09360168073125158</v>
       </c>
       <c r="FB14" t="n">
-        <v>0.007837215839428587</v>
+        <v>-0.01456453096897911</v>
       </c>
       <c r="FC14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FD14" t="n">
         <v>0</v>
       </c>
       <c r="FE14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FG14" t="n">
         <v>0</v>
       </c>
       <c r="FH14" t="n">
-        <v>-0.03391642873225893</v>
+        <v>0.08495852283241145</v>
       </c>
       <c r="FI14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ14" t="n">
-        <v>0.009748860922205853</v>
+        <v>0.06588784209648087</v>
       </c>
       <c r="FK14" t="n">
-        <v>0.04003038956592191</v>
+        <v>-0.02927234062714132</v>
       </c>
       <c r="FL14" t="n">
         <v>-0</v>
@@ -8334,28 +8334,28 @@
         <v>0</v>
       </c>
       <c r="FN14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FP14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FQ14" t="n">
-        <v>-0.001325058454232322</v>
+        <v>0.0006446867539111021</v>
       </c>
       <c r="FR14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS14" t="n">
-        <v>0.003346667008543039</v>
+        <v>0.08639554229241743</v>
       </c>
       <c r="FT14" t="n">
-        <v>-0.005775166050470295</v>
+        <v>-0.01727612202708984</v>
       </c>
       <c r="FU14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FV14" t="n">
         <v>0</v>
@@ -8367,39 +8367,39 @@
         <v>0</v>
       </c>
       <c r="FY14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ14" t="n">
-        <v>0.02257652514041972</v>
+        <v>-0.01366722903743068</v>
       </c>
       <c r="GA14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB14" t="n">
-        <v>-0.085187614260617</v>
+        <v>0.0258604532569747</v>
       </c>
       <c r="GC14" t="n">
         <v>-0</v>
       </c>
       <c r="GD14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GE14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF14" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GG14" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="B15" t="n">
-        <v>0.3270061975876245</v>
+        <v>0.4015879358322397</v>
       </c>
       <c r="C15" t="n">
         <v>0</v>
@@ -8408,10 +8408,10 @@
         <v>0</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.08896715240750655</v>
+        <v>-0.0001882057447845785</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.2158640818302616</v>
+        <v>-0.3422955556509796</v>
       </c>
       <c r="G15" t="n">
         <v>-0</v>
@@ -8420,13 +8420,13 @@
         <v>-0</v>
       </c>
       <c r="I15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3103632988364848</v>
+        <v>0.5606472512156052</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -8435,25 +8435,25 @@
         <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.02850021387719847</v>
+        <v>-0.07919614953543239</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.2229273735923359</v>
+        <v>-0.4770548975740098</v>
       </c>
       <c r="P15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.03962797669571628</v>
+        <v>0.1627048036281291</v>
       </c>
       <c r="U15" t="n">
         <v>0</v>
@@ -8462,37 +8462,37 @@
         <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.02706734574189182</v>
+        <v>-0.100516856780441</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.01149821315342154</v>
+        <v>-0.07681069439391298</v>
       </c>
       <c r="Y15" t="n">
         <v>-0</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AB15" t="n">
         <v>-0</v>
       </c>
       <c r="AC15" t="n">
-        <v>0.007460433677973328</v>
+        <v>-0.02146908679322361</v>
       </c>
       <c r="AD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AE15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0.03104874100264686</v>
+        <v>-0.3231835310994855</v>
       </c>
       <c r="AG15" t="n">
-        <v>0.007016606274025094</v>
+        <v>0.09822810317314436</v>
       </c>
       <c r="AH15" t="n">
         <v>-0</v>
@@ -8501,28 +8501,28 @@
         <v>-0</v>
       </c>
       <c r="AJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AL15" t="n">
-        <v>0.04973740039457255</v>
+        <v>0.1274165660415132</v>
       </c>
       <c r="AM15" t="n">
         <v>-0</v>
       </c>
       <c r="AN15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO15" t="n">
-        <v>-0.003414382254529652</v>
+        <v>-0.07569000952853519</v>
       </c>
       <c r="AP15" t="n">
-        <v>-0.07427894615197138</v>
+        <v>-0.08570097939008484</v>
       </c>
       <c r="AQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR15" t="n">
         <v>-0</v>
@@ -8531,37 +8531,37 @@
         <v>0</v>
       </c>
       <c r="AT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.2473136761282198</v>
+        <v>0.7103432133705951</v>
       </c>
       <c r="AV15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX15" t="n">
-        <v>-0.02703313644466197</v>
+        <v>-0.3200330369759922</v>
       </c>
       <c r="AY15" t="n">
-        <v>-0.0856595152129732</v>
+        <v>-0.2050850564224694</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BD15" t="n">
-        <v>0.07255580731143055</v>
+        <v>-0.1265820638866519</v>
       </c>
       <c r="BE15" t="n">
         <v>0</v>
@@ -8570,25 +8570,25 @@
         <v>0</v>
       </c>
       <c r="BG15" t="n">
-        <v>-0.06576769046280416</v>
+        <v>-0.02412870640013874</v>
       </c>
       <c r="BH15" t="n">
-        <v>-0.08846981214792121</v>
+        <v>-0.03749282787907415</v>
       </c>
       <c r="BI15" t="n">
         <v>0</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.06227753872661084</v>
+        <v>0.1405754899757987</v>
       </c>
       <c r="BN15" t="n">
         <v>-0</v>
@@ -8597,37 +8597,37 @@
         <v>-0</v>
       </c>
       <c r="BP15" t="n">
-        <v>0.01810381293350538</v>
+        <v>0.07798654766294806</v>
       </c>
       <c r="BQ15" t="n">
-        <v>0.01864966166978327</v>
+        <v>0.03822615613975494</v>
       </c>
       <c r="BR15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS15" t="n">
         <v>-0</v>
       </c>
       <c r="BT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV15" t="n">
-        <v>0.1326663733927211</v>
+        <v>0.4029047270374253</v>
       </c>
       <c r="BW15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BX15" t="n">
         <v>0</v>
       </c>
       <c r="BY15" t="n">
-        <v>-0.04414900240911659</v>
+        <v>-0.04756815935078262</v>
       </c>
       <c r="BZ15" t="n">
-        <v>-0.04832743820775708</v>
+        <v>-0.1879791455927431</v>
       </c>
       <c r="CA15" t="n">
         <v>-0</v>
@@ -8636,28 +8636,28 @@
         <v>-0</v>
       </c>
       <c r="CC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD15" t="n">
         <v>0</v>
       </c>
       <c r="CE15" t="n">
-        <v>-0.06799653321921585</v>
+        <v>-0.1542639096692359</v>
       </c>
       <c r="CF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG15" t="n">
         <v>-0</v>
       </c>
       <c r="CH15" t="n">
-        <v>-0.007754356771684821</v>
+        <v>0.04003815383036168</v>
       </c>
       <c r="CI15" t="n">
-        <v>0.04472624179740071</v>
+        <v>0.1102257639806059</v>
       </c>
       <c r="CJ15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK15" t="n">
         <v>0</v>
@@ -8669,49 +8669,49 @@
         <v>0</v>
       </c>
       <c r="CN15" t="n">
-        <v>-0.003106679741743236</v>
+        <v>-0.1799327466143662</v>
       </c>
       <c r="CO15" t="n">
         <v>-0</v>
       </c>
       <c r="CP15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ15" t="n">
-        <v>-0.02338628604142299</v>
+        <v>0.1430137008025651</v>
       </c>
       <c r="CR15" t="n">
-        <v>-0.07379886511405619</v>
+        <v>0.03970268200960417</v>
       </c>
       <c r="CS15" t="n">
         <v>-0</v>
       </c>
       <c r="CT15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV15" t="n">
         <v>-0</v>
       </c>
       <c r="CW15" t="n">
-        <v>-0.06107179913725279</v>
+        <v>-0.1460944324662869</v>
       </c>
       <c r="CX15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY15" t="n">
         <v>0</v>
       </c>
       <c r="CZ15" t="n">
-        <v>-0.007787277786378805</v>
+        <v>0.02305537221882287</v>
       </c>
       <c r="DA15" t="n">
-        <v>0.04711530222866236</v>
+        <v>0.1440317130117701</v>
       </c>
       <c r="DB15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC15" t="n">
         <v>-0</v>
@@ -8723,19 +8723,19 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>-0.05243375882188207</v>
+        <v>-0.1066935756049994</v>
       </c>
       <c r="DG15" t="n">
         <v>0</v>
       </c>
       <c r="DH15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.06343444896983677</v>
+        <v>-0.07301248536587231</v>
       </c>
       <c r="DJ15" t="n">
-        <v>0.05127708252545429</v>
+        <v>0.08213527375141255</v>
       </c>
       <c r="DK15" t="n">
         <v>0</v>
@@ -8744,13 +8744,13 @@
         <v>0</v>
       </c>
       <c r="DM15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DN15" t="n">
         <v>-0</v>
       </c>
       <c r="DO15" t="n">
-        <v>-0.02053390920616312</v>
+        <v>-0.07390425868674068</v>
       </c>
       <c r="DP15" t="n">
         <v>0</v>
@@ -8759,16 +8759,16 @@
         <v>0</v>
       </c>
       <c r="DR15" t="n">
-        <v>0.02847861098977629</v>
+        <v>-0.006509586504683862</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.01410245095436079</v>
+        <v>0.099499100330007</v>
       </c>
       <c r="DT15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DU15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV15" t="n">
         <v>0</v>
@@ -8777,76 +8777,76 @@
         <v>-0</v>
       </c>
       <c r="DX15" t="n">
-        <v>-0.06072310049753631</v>
+        <v>-0.06332214758088676</v>
       </c>
       <c r="DY15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA15" t="n">
-        <v>0.01827710642040244</v>
+        <v>-0.009372170108718391</v>
       </c>
       <c r="EB15" t="n">
-        <v>0.03025763699963034</v>
+        <v>0.03926002827857847</v>
       </c>
       <c r="EC15" t="n">
         <v>-0</v>
       </c>
       <c r="ED15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF15" t="n">
         <v>0</v>
       </c>
       <c r="EG15" t="n">
-        <v>-0.0748881364524792</v>
+        <v>-0.03824657084447471</v>
       </c>
       <c r="EH15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EI15" t="n">
         <v>-0</v>
       </c>
       <c r="EJ15" t="n">
-        <v>0.03065247630772401</v>
+        <v>-0.01099905053334348</v>
       </c>
       <c r="EK15" t="n">
-        <v>0.03353200560139591</v>
+        <v>0.01942293605795607</v>
       </c>
       <c r="EL15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM15" t="n">
         <v>-0</v>
       </c>
       <c r="EN15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO15" t="n">
         <v>0</v>
       </c>
       <c r="EP15" t="n">
-        <v>-0.04691657753268808</v>
+        <v>-0.05411049538857834</v>
       </c>
       <c r="EQ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER15" t="n">
         <v>-0</v>
       </c>
       <c r="ES15" t="n">
-        <v>-0.04136522695662299</v>
+        <v>-0.08519216887380864</v>
       </c>
       <c r="ET15" t="n">
-        <v>0.007335051385062643</v>
+        <v>-0.01685535148772703</v>
       </c>
       <c r="EU15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV15" t="n">
         <v>0</v>
@@ -8858,46 +8858,46 @@
         <v>0</v>
       </c>
       <c r="EY15" t="n">
-        <v>-0.06340822179503749</v>
+        <v>-0.1762360281984073</v>
       </c>
       <c r="EZ15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA15" t="n">
         <v>-0</v>
       </c>
       <c r="FB15" t="n">
-        <v>-0.003152470826970344</v>
+        <v>-0.002137168163514947</v>
       </c>
       <c r="FC15" t="n">
-        <v>0.04824617278321801</v>
+        <v>0.1230235973154088</v>
       </c>
       <c r="FD15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE15" t="n">
         <v>0</v>
       </c>
       <c r="FF15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG15" t="n">
         <v>0</v>
       </c>
       <c r="FH15" t="n">
-        <v>-0.0293547223353519</v>
+        <v>0.1360300182402241</v>
       </c>
       <c r="FI15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ15" t="n">
         <v>-0</v>
       </c>
       <c r="FK15" t="n">
-        <v>0.005373695126452929</v>
+        <v>-0.08594624880855678</v>
       </c>
       <c r="FL15" t="n">
-        <v>0.04135195473229911</v>
+        <v>0.1898006867657189</v>
       </c>
       <c r="FM15" t="n">
         <v>0</v>
@@ -8912,7 +8912,7 @@
         <v>0</v>
       </c>
       <c r="FQ15" t="n">
-        <v>-0.001427673693359327</v>
+        <v>0.01414632595351415</v>
       </c>
       <c r="FR15" t="n">
         <v>-0</v>
@@ -8921,37 +8921,37 @@
         <v>-0</v>
       </c>
       <c r="FT15" t="n">
-        <v>-0.002836561464883065</v>
+        <v>-0.01081117184991514</v>
       </c>
       <c r="FU15" t="n">
-        <v>0.04859032408504889</v>
+        <v>-0.07873731441605294</v>
       </c>
       <c r="FV15" t="n">
         <v>-0</v>
       </c>
       <c r="FW15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ15" t="n">
-        <v>0.009923257485090618</v>
+        <v>-0.0321722374902771</v>
       </c>
       <c r="GA15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB15" t="n">
         <v>-0</v>
       </c>
       <c r="GC15" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD15" t="n">
-        <v>-0.05077214274318714</v>
+        <v>0.1728423619044678</v>
       </c>
       <c r="GE15" t="n">
         <v>-0</v>
@@ -8960,7 +8960,7 @@
         <v>-0</v>
       </c>
       <c r="GG15" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -8968,7 +8968,7 @@
         <v>0</v>
       </c>
       <c r="B16" t="n">
-        <v>0.5792437066328294</v>
+        <v>0.3563346611196312</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
@@ -8977,16 +8977,16 @@
         <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.1274810186006819</v>
+        <v>-0.03092164831917627</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.5091105243607013</v>
+        <v>-0.1426984252606821</v>
       </c>
       <c r="G16" t="n">
         <v>-0</v>
       </c>
       <c r="H16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
@@ -8995,7 +8995,7 @@
         <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>0.5760069712492182</v>
+        <v>0.5036583725829984</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -9004,25 +9004,25 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.05813319017185963</v>
+        <v>-0.1219332840142775</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.5537183048372705</v>
+        <v>-0.2176796523836552</v>
       </c>
       <c r="P16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
       </c>
       <c r="S16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0.04755236829990615</v>
+        <v>0.1064887658080962</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
@@ -9031,37 +9031,37 @@
         <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.110654745010335</v>
+        <v>-0.1166618233662825</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.02565384337818499</v>
+        <v>-0.005090410387975141</v>
       </c>
       <c r="Y16" t="n">
         <v>-0</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA16" t="n">
         <v>0</v>
       </c>
       <c r="AB16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC16" t="n">
-        <v>-0.0275390229202471</v>
+        <v>-0.02931597959110936</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AE16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>-0.0215953269672738</v>
+        <v>-0.2716371709374638</v>
       </c>
       <c r="AG16" t="n">
-        <v>-0.04212379964103503</v>
+        <v>-0.004549947446162852</v>
       </c>
       <c r="AH16" t="n">
         <v>-0</v>
@@ -9076,7 +9076,7 @@
         <v>0</v>
       </c>
       <c r="AL16" t="n">
-        <v>0.09769455732862328</v>
+        <v>0.03627142449193518</v>
       </c>
       <c r="AM16" t="n">
         <v>-0</v>
@@ -9085,10 +9085,10 @@
         <v>0</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.0006567358219328438</v>
+        <v>-0.03902280683020567</v>
       </c>
       <c r="AP16" t="n">
-        <v>-0.09125932246545443</v>
+        <v>0.0179704578611553</v>
       </c>
       <c r="AQ16" t="n">
         <v>-0</v>
@@ -9100,10 +9100,10 @@
         <v>0</v>
       </c>
       <c r="AT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.4681216858609668</v>
+        <v>0.4830067608289389</v>
       </c>
       <c r="AV16" t="n">
         <v>-0</v>
@@ -9112,16 +9112,16 @@
         <v>0</v>
       </c>
       <c r="AX16" t="n">
-        <v>-0.07547865179868263</v>
+        <v>-0.2471306261364534</v>
       </c>
       <c r="AY16" t="n">
-        <v>-0.2411337016768416</v>
+        <v>-0.1030859309087518</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BB16" t="n">
         <v>0</v>
@@ -9130,7 +9130,7 @@
         <v>0</v>
       </c>
       <c r="BD16" t="n">
-        <v>0.1256404465667237</v>
+        <v>-0.02640743229741034</v>
       </c>
       <c r="BE16" t="n">
         <v>0</v>
@@ -9139,52 +9139,52 @@
         <v>0</v>
       </c>
       <c r="BG16" t="n">
-        <v>-0.1561352566964735</v>
+        <v>-0.01826023118805718</v>
       </c>
       <c r="BH16" t="n">
-        <v>-0.2061257706689008</v>
+        <v>-0.08055430902221697</v>
       </c>
       <c r="BI16" t="n">
         <v>-0</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK16" t="n">
         <v>0</v>
       </c>
       <c r="BL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.1601394364002145</v>
+        <v>0.05420754045649814</v>
       </c>
       <c r="BN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BO16" t="n">
         <v>-0</v>
       </c>
       <c r="BP16" t="n">
-        <v>-0.001140776253103799</v>
+        <v>0.07284421821868936</v>
       </c>
       <c r="BQ16" t="n">
-        <v>0.01590004500465311</v>
+        <v>-0.03856732649621976</v>
       </c>
       <c r="BR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU16" t="n">
         <v>-0</v>
       </c>
       <c r="BV16" t="n">
-        <v>0.2485805446403976</v>
+        <v>0.2599856884467435</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
@@ -9193,10 +9193,10 @@
         <v>0</v>
       </c>
       <c r="BY16" t="n">
-        <v>-0.07451044470466224</v>
+        <v>-0.07364203894135758</v>
       </c>
       <c r="BZ16" t="n">
-        <v>-0.1461459617618215</v>
+        <v>-0.09421125771368159</v>
       </c>
       <c r="CA16" t="n">
         <v>-0</v>
@@ -9205,28 +9205,28 @@
         <v>-0</v>
       </c>
       <c r="CC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CD16" t="n">
         <v>-0</v>
       </c>
       <c r="CE16" t="n">
-        <v>-0.09586491076524317</v>
+        <v>-0.1098733076809664</v>
       </c>
       <c r="CF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG16" t="n">
         <v>-0</v>
       </c>
       <c r="CH16" t="n">
-        <v>-0.006446215008329582</v>
+        <v>0.02944543385110552</v>
       </c>
       <c r="CI16" t="n">
-        <v>0.1165299558341483</v>
+        <v>0.04753346200453771</v>
       </c>
       <c r="CJ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK16" t="n">
         <v>0</v>
@@ -9238,100 +9238,100 @@
         <v>0</v>
       </c>
       <c r="CN16" t="n">
-        <v>-0.003115304557728661</v>
+        <v>-0.132883428025923</v>
       </c>
       <c r="CO16" t="n">
         <v>-0</v>
       </c>
       <c r="CP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ16" t="n">
-        <v>0.01787048106919314</v>
+        <v>0.1103401426896391</v>
       </c>
       <c r="CR16" t="n">
-        <v>-0.02395170569775671</v>
+        <v>0.1006350723349099</v>
       </c>
       <c r="CS16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CW16" t="n">
-        <v>-0.07769714451202178</v>
+        <v>-0.1101429362917546</v>
       </c>
       <c r="CX16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY16" t="n">
         <v>0</v>
       </c>
       <c r="CZ16" t="n">
-        <v>-0.005546675415865648</v>
+        <v>0.008845732805488119</v>
       </c>
       <c r="DA16" t="n">
-        <v>0.121821495728354</v>
+        <v>0.06877497437296268</v>
       </c>
       <c r="DB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC16" t="n">
         <v>-0</v>
       </c>
       <c r="DD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE16" t="n">
         <v>0</v>
       </c>
       <c r="DF16" t="n">
-        <v>-0.04474311101682561</v>
+        <v>-0.04971666937476797</v>
       </c>
       <c r="DG16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05347417951927155</v>
+        <v>-0.168019676363107</v>
       </c>
       <c r="DJ16" t="n">
-        <v>-0.001451015452034701</v>
+        <v>0.04964933054648572</v>
       </c>
       <c r="DK16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DM16" t="n">
         <v>0</v>
       </c>
       <c r="DN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO16" t="n">
-        <v>0.003472330483317901</v>
+        <v>-0.01092191807312633</v>
       </c>
       <c r="DP16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DR16" t="n">
-        <v>0.03362394520549131</v>
+        <v>-0.05045557676934236</v>
       </c>
       <c r="DS16" t="n">
-        <v>-0.007595696074924218</v>
+        <v>0.06265048639325359</v>
       </c>
       <c r="DT16" t="n">
         <v>-0</v>
@@ -9340,13 +9340,13 @@
         <v>-0</v>
       </c>
       <c r="DV16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW16" t="n">
         <v>-0</v>
       </c>
       <c r="DX16" t="n">
-        <v>-0.06633790709106792</v>
+        <v>-0.02029626083507293</v>
       </c>
       <c r="DY16" t="n">
         <v>0</v>
@@ -9355,25 +9355,25 @@
         <v>-0</v>
       </c>
       <c r="EA16" t="n">
-        <v>0.02092571729254978</v>
+        <v>-0.07606006179769176</v>
       </c>
       <c r="EB16" t="n">
-        <v>0.0604119105792296</v>
+        <v>0.02755687738840463</v>
       </c>
       <c r="EC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ED16" t="n">
         <v>0</v>
       </c>
       <c r="EE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG16" t="n">
-        <v>-0.108232070485527</v>
+        <v>-0.04202635601058043</v>
       </c>
       <c r="EH16" t="n">
         <v>0</v>
@@ -9382,79 +9382,79 @@
         <v>-0</v>
       </c>
       <c r="EJ16" t="n">
-        <v>0.02331439806358535</v>
+        <v>0.02215210337803252</v>
       </c>
       <c r="EK16" t="n">
-        <v>0.1265440928468862</v>
+        <v>-0.009410661920081128</v>
       </c>
       <c r="EL16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM16" t="n">
         <v>-0</v>
       </c>
       <c r="EN16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EO16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EP16" t="n">
-        <v>-0.03263884978846953</v>
+        <v>-0.01312609594229622</v>
       </c>
       <c r="EQ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER16" t="n">
         <v>-0</v>
       </c>
       <c r="ES16" t="n">
-        <v>-0.0146199236652245</v>
+        <v>-0.01706506412837016</v>
       </c>
       <c r="ET16" t="n">
-        <v>0.07942412872194721</v>
+        <v>0.1215373664251312</v>
       </c>
       <c r="EU16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV16" t="n">
         <v>0</v>
       </c>
       <c r="EW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY16" t="n">
-        <v>-0.07440339027998528</v>
+        <v>-0.1296503996940592</v>
       </c>
       <c r="EZ16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA16" t="n">
         <v>-0</v>
       </c>
       <c r="FB16" t="n">
-        <v>0.005603887711857129</v>
+        <v>0.000249308693892745</v>
       </c>
       <c r="FC16" t="n">
-        <v>0.1105132503528639</v>
+        <v>0.03831841965707554</v>
       </c>
       <c r="FD16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FF16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG16" t="n">
         <v>0</v>
       </c>
       <c r="FH16" t="n">
-        <v>-0.003945683446421438</v>
+        <v>0.1922076591772191</v>
       </c>
       <c r="FI16" t="n">
         <v>-0</v>
@@ -9463,16 +9463,16 @@
         <v>-0</v>
       </c>
       <c r="FK16" t="n">
-        <v>-0.0100714325585216</v>
+        <v>-0.09426401307233671</v>
       </c>
       <c r="FL16" t="n">
-        <v>0.05596894958747622</v>
+        <v>0.109675009652774</v>
       </c>
       <c r="FM16" t="n">
         <v>0</v>
       </c>
       <c r="FN16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO16" t="n">
         <v>0</v>
@@ -9481,46 +9481,46 @@
         <v>0</v>
       </c>
       <c r="FQ16" t="n">
-        <v>0.005437178968010783</v>
+        <v>0.009855611703085876</v>
       </c>
       <c r="FR16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS16" t="n">
         <v>-0</v>
       </c>
       <c r="FT16" t="n">
-        <v>-0.009291071496026496</v>
+        <v>-0.0251904100577068</v>
       </c>
       <c r="FU16" t="n">
-        <v>0.03707465793457311</v>
+        <v>-0.05046906775903426</v>
       </c>
       <c r="FV16" t="n">
         <v>-0</v>
       </c>
       <c r="FW16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ16" t="n">
-        <v>0.05130643391850202</v>
+        <v>-0.03420563764413689</v>
       </c>
       <c r="GA16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GC16" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD16" t="n">
-        <v>-0.05910585980061403</v>
+        <v>0.05732790399884384</v>
       </c>
       <c r="GE16" t="n">
         <v>-0</v>
@@ -9529,7 +9529,7 @@
         <v>-0</v>
       </c>
       <c r="GG16" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -10675,7 +10675,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1544188935148341</v>
+        <v>0.3958643794029042</v>
       </c>
       <c r="C19" t="n">
         <v>0</v>
@@ -10684,25 +10684,25 @@
         <v>0</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.07434624519471678</v>
+        <v>-0.02084509152020293</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.07191094627322574</v>
+        <v>-0.1446385525758582</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H19" t="n">
         <v>-0</v>
       </c>
       <c r="I19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.1313128974087503</v>
+        <v>0.4986440986933964</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -10711,25 +10711,25 @@
         <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.05300828472760943</v>
+        <v>-0.1279690718404325</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.07991690897304321</v>
+        <v>-0.2041604031644494</v>
       </c>
       <c r="P19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="T19" t="n">
-        <v>0.01285498906148165</v>
+        <v>0.08982252365081479</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -10738,40 +10738,40 @@
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.009143915894461702</v>
+        <v>-0.0746323075620289</v>
       </c>
       <c r="X19" t="n">
-        <v>0.008585893434490358</v>
+        <v>-0.009302112134788276</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AA19" t="n">
         <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>-0.00708099261352923</v>
+        <v>-0.03024932641232912</v>
       </c>
       <c r="AD19" t="n">
         <v>-0</v>
       </c>
       <c r="AE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.01095058767563661</v>
+        <v>-0.2307873373409146</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.008891241431807639</v>
+        <v>0.01709925190226669</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI19" t="n">
         <v>-0</v>
@@ -10783,22 +10783,22 @@
         <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.009017842687066626</v>
+        <v>0.04035664814959713</v>
       </c>
       <c r="AM19" t="n">
         <v>-0</v>
       </c>
       <c r="AN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>-0.008681091507523003</v>
+        <v>-0.02778306521480335</v>
       </c>
       <c r="AP19" t="n">
-        <v>-0.01371395358608961</v>
+        <v>-0.0001885847210065052</v>
       </c>
       <c r="AQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AR19" t="n">
         <v>-0</v>
@@ -10807,25 +10807,25 @@
         <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>0.09654125682359209</v>
+        <v>0.3938336471289925</v>
       </c>
       <c r="AV19" t="n">
         <v>-0</v>
       </c>
       <c r="AW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>-0.02558823624540049</v>
+        <v>-0.2563008768056509</v>
       </c>
       <c r="AY19" t="n">
-        <v>-0.01930057289415121</v>
+        <v>-0.1024042275531773</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BA19" t="n">
         <v>-0</v>
@@ -10837,7 +10837,7 @@
         <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>0.0302820312550028</v>
+        <v>0.00252955785861262</v>
       </c>
       <c r="BE19" t="n">
         <v>0</v>
@@ -10846,52 +10846,52 @@
         <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>-0.04866486776021819</v>
+        <v>-0.002904869744809502</v>
       </c>
       <c r="BH19" t="n">
-        <v>-0.0543366550675645</v>
+        <v>-0.04804601829997016</v>
       </c>
       <c r="BI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BK19" t="n">
         <v>0</v>
       </c>
       <c r="BL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.03448809281252849</v>
+        <v>0.03959616992019722</v>
       </c>
       <c r="BN19" t="n">
         <v>-0</v>
       </c>
       <c r="BO19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BP19" t="n">
-        <v>0.01721900225294691</v>
+        <v>0.04865757265505019</v>
       </c>
       <c r="BQ19" t="n">
-        <v>0.01589760666920734</v>
+        <v>-0.02422771510152101</v>
       </c>
       <c r="BR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BS19" t="n">
         <v>-0</v>
       </c>
       <c r="BT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="BV19" t="n">
-        <v>0.04605661846881794</v>
+        <v>0.2209306048771014</v>
       </c>
       <c r="BW19" t="n">
         <v>0</v>
@@ -10900,10 +10900,10 @@
         <v>0</v>
       </c>
       <c r="BY19" t="n">
-        <v>-0.01045136467074858</v>
+        <v>-0.05304717578285637</v>
       </c>
       <c r="BZ19" t="n">
-        <v>-0.01144505830400866</v>
+        <v>-0.09802608447146666</v>
       </c>
       <c r="CA19" t="n">
         <v>-0</v>
@@ -10915,28 +10915,28 @@
         <v>-0</v>
       </c>
       <c r="CD19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CE19" t="n">
-        <v>-0.02315840521840748</v>
+        <v>-0.1034167076342855</v>
       </c>
       <c r="CF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CG19" t="n">
         <v>-0</v>
       </c>
       <c r="CH19" t="n">
-        <v>0.006584241803874971</v>
+        <v>0.02809609202439048</v>
       </c>
       <c r="CI19" t="n">
-        <v>0.01672923858127688</v>
+        <v>0.05187316016624946</v>
       </c>
       <c r="CJ19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CK19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CL19" t="n">
         <v>0</v>
@@ -10945,76 +10945,76 @@
         <v>0</v>
       </c>
       <c r="CN19" t="n">
-        <v>0.001485202031397698</v>
+        <v>-0.1324474891003564</v>
       </c>
       <c r="CO19" t="n">
         <v>-0</v>
       </c>
       <c r="CP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CQ19" t="n">
-        <v>-0.0073279866417078</v>
+        <v>0.1474936523834096</v>
       </c>
       <c r="CR19" t="n">
-        <v>-0.01263667932660277</v>
+        <v>0.06768225135802683</v>
       </c>
       <c r="CS19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CT19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="CV19" t="n">
         <v>-0</v>
       </c>
       <c r="CW19" t="n">
-        <v>-0.01765724039905513</v>
+        <v>-0.1010686269832201</v>
       </c>
       <c r="CX19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="CY19" t="n">
         <v>0</v>
       </c>
       <c r="CZ19" t="n">
-        <v>0.005379815246833458</v>
+        <v>0.015331665117897</v>
       </c>
       <c r="DA19" t="n">
-        <v>0.01733536584598776</v>
+        <v>0.07164908613476234</v>
       </c>
       <c r="DB19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DE19" t="n">
         <v>0</v>
       </c>
       <c r="DF19" t="n">
-        <v>-0.0301532257095577</v>
+        <v>-0.08033913368697386</v>
       </c>
       <c r="DG19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.04821482242880116</v>
+        <v>-0.1956340256185488</v>
       </c>
       <c r="DJ19" t="n">
-        <v>0.01088256427121481</v>
+        <v>0.06007360194547549</v>
       </c>
       <c r="DK19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DL19" t="n">
         <v>-0</v>
@@ -11023,79 +11023,79 @@
         <v>0</v>
       </c>
       <c r="DN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DO19" t="n">
-        <v>-0.005855340341051488</v>
+        <v>-0.01837878589909518</v>
       </c>
       <c r="DP19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DQ19" t="n">
         <v>0</v>
       </c>
       <c r="DR19" t="n">
-        <v>0.02068669027473315</v>
+        <v>-0.03498485093664613</v>
       </c>
       <c r="DS19" t="n">
-        <v>-0.007959741920477664</v>
+        <v>0.02766281593663096</v>
       </c>
       <c r="DT19" t="n">
         <v>-0</v>
       </c>
       <c r="DU19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DV19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DW19" t="n">
         <v>-0</v>
       </c>
       <c r="DX19" t="n">
-        <v>-0.02656132921347498</v>
+        <v>-0.006562249680281331</v>
       </c>
       <c r="DY19" t="n">
         <v>0</v>
       </c>
       <c r="DZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EA19" t="n">
-        <v>0.01415902346671893</v>
+        <v>-0.06639004196760329</v>
       </c>
       <c r="EB19" t="n">
-        <v>0.01832937144328398</v>
+        <v>0.0166167110461417</v>
       </c>
       <c r="EC19" t="n">
         <v>-0</v>
       </c>
       <c r="ED19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EG19" t="n">
-        <v>-0.02815144169986555</v>
+        <v>-0.04669363257947479</v>
       </c>
       <c r="EH19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EI19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EJ19" t="n">
-        <v>0.006443556042594025</v>
+        <v>0.01152574949112689</v>
       </c>
       <c r="EK19" t="n">
-        <v>0.01244994054135613</v>
+        <v>0.004292513796186449</v>
       </c>
       <c r="EL19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EM19" t="n">
         <v>-0</v>
@@ -11107,79 +11107,79 @@
         <v>0</v>
       </c>
       <c r="EP19" t="n">
-        <v>-0.009990529301953644</v>
+        <v>-0.04251452547465764</v>
       </c>
       <c r="EQ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ER19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="ES19" t="n">
-        <v>0.002515272087712165</v>
+        <v>-0.0155457864232985</v>
       </c>
       <c r="ET19" t="n">
-        <v>-0.009720591527442599</v>
+        <v>0.0860015087308605</v>
       </c>
       <c r="EU19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EV19" t="n">
         <v>0</v>
       </c>
       <c r="EW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="EX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="EY19" t="n">
-        <v>-0.01816137902611428</v>
+        <v>-0.1214162651914464</v>
       </c>
       <c r="EZ19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FA19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FB19" t="n">
-        <v>0.008609350245061197</v>
+        <v>0.002555874606952007</v>
       </c>
       <c r="FC19" t="n">
-        <v>0.0205748469995555</v>
+        <v>0.04479780620918175</v>
       </c>
       <c r="FD19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FE19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FF19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FG19" t="n">
         <v>0</v>
       </c>
       <c r="FH19" t="n">
-        <v>-0.01363540422291733</v>
+        <v>0.1511574967464079</v>
       </c>
       <c r="FI19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FJ19" t="n">
         <v>-0</v>
       </c>
       <c r="FK19" t="n">
-        <v>0.01161635186728579</v>
+        <v>-0.08862515265782175</v>
       </c>
       <c r="FL19" t="n">
-        <v>0.01895218087121359</v>
+        <v>0.109636536573462</v>
       </c>
       <c r="FM19" t="n">
         <v>0</v>
       </c>
       <c r="FN19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FO19" t="n">
         <v>0</v>
@@ -11188,55 +11188,55 @@
         <v>0</v>
       </c>
       <c r="FQ19" t="n">
-        <v>6.383140881813266e-05</v>
+        <v>0.00150547842735951</v>
       </c>
       <c r="FR19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FS19" t="n">
         <v>-0</v>
       </c>
       <c r="FT19" t="n">
-        <v>-0.001260441709090497</v>
+        <v>-0.009248608646502012</v>
       </c>
       <c r="FU19" t="n">
-        <v>0.01957513267543856</v>
+        <v>-0.0243058301229967</v>
       </c>
       <c r="FV19" t="n">
         <v>0</v>
       </c>
       <c r="FW19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FX19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="FY19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="FZ19" t="n">
-        <v>0.003079416305427231</v>
+        <v>-0.02878331499979738</v>
       </c>
       <c r="GA19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="GB19" t="n">
         <v>-0</v>
       </c>
       <c r="GC19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GD19" t="n">
-        <v>-0.0048316269926084</v>
+        <v>0.0646616299022493</v>
       </c>
       <c r="GE19" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="GF19" t="n">
         <v>-0</v>
       </c>
       <c r="GG19" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
